--- a/Справка/База договоров.xlsx
+++ b/Справка/База договоров.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1259"/>
+  <dimension ref="A1:Q1356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="12.5" customWidth="1" style="1" min="1" max="1"/>
@@ -7364,6 +7364,11 @@
       <c r="O92" s="8" t="n">
         <v>767</v>
       </c>
+      <c r="P92" s="8" t="inlineStr">
+        <is>
+          <t>06066249-0c8f-472f-9e1b-257cbc41d124</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -11066,6 +11071,9 @@
           <t>Нет</t>
         </is>
       </c>
+      <c r="O142" t="n">
+        <v>2870</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
@@ -12017,6 +12025,12 @@
           <t>Нет</t>
         </is>
       </c>
+      <c r="O155" t="n">
+        <v>1193</v>
+      </c>
+      <c r="P155" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
@@ -22375,6 +22389,11 @@
       <c r="O293" s="8" t="n">
         <v>36102</v>
       </c>
+      <c r="P293" s="8" t="inlineStr">
+        <is>
+          <t>9b152b8f-140e-4c9f-9fb4-603c415150a6</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="8" t="inlineStr">
@@ -24567,6 +24586,11 @@
       <c r="O323" s="8" t="n">
         <v>3388</v>
       </c>
+      <c r="P323" s="8" t="inlineStr">
+        <is>
+          <t>0c509815-56bf-4ddc-936c-8b0e07a98c30</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="8" t="inlineStr">
@@ -24713,6 +24737,11 @@
       <c r="O325" s="8" t="n">
         <v>48008</v>
       </c>
+      <c r="P325" s="8" t="inlineStr">
+        <is>
+          <t>c20d14d1-dbcb-4ab4-a744-534a4920d857</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="8" t="inlineStr">
@@ -25224,6 +25253,11 @@
       <c r="O332" s="8" t="n">
         <v>49570</v>
       </c>
+      <c r="P332" s="8" t="inlineStr">
+        <is>
+          <t>d86bb633-e192-48bb-8075-029d49510138</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="8" t="inlineStr">
@@ -28721,6 +28755,11 @@
       <c r="O380" s="8" t="n">
         <v>58030</v>
       </c>
+      <c r="P380" s="8" t="inlineStr">
+        <is>
+          <t>65188400-795d-4a0f-8d7b-dc502f66d26d</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="8" t="inlineStr">
@@ -29808,6 +29847,11 @@
       <c r="O395" s="8" t="n">
         <v>53064</v>
       </c>
+      <c r="P395" s="8" t="inlineStr">
+        <is>
+          <t>d9079394-c22f-4dbf-8556-e79f00830ba4</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="8" t="inlineStr">
@@ -30611,6 +30655,11 @@
       <c r="O406" s="8" t="n">
         <v>62720</v>
       </c>
+      <c r="P406" s="8" t="inlineStr">
+        <is>
+          <t>273645fc-0d01-4755-80f6-8344b3ff74c0</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="8" t="inlineStr">
@@ -32801,6 +32850,11 @@
       <c r="O436" s="8" t="n">
         <v>91883</v>
       </c>
+      <c r="P436" s="8" t="inlineStr">
+        <is>
+          <t>45cc3ec4-2ddc-40ba-89d1-fc171933a09a</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="8" t="inlineStr">
@@ -37006,6 +37060,11 @@
       <c r="O494" s="8" t="n">
         <v>94331</v>
       </c>
+      <c r="P494" s="8" t="inlineStr">
+        <is>
+          <t>dd19b46d-c6ef-4c3b-b502-935b8fff22a9</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="8" t="inlineStr">
@@ -38452,6 +38511,11 @@
       <c r="O514" s="8" t="n">
         <v>89618</v>
       </c>
+      <c r="P514" s="8" t="inlineStr">
+        <is>
+          <t>ce6f277f-e9cf-42b2-a7ea-261000c81ffd</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="8" t="inlineStr">
@@ -39323,6 +39387,11 @@
       <c r="O526" s="8" t="n">
         <v>498</v>
       </c>
+      <c r="P526" s="8" t="inlineStr">
+        <is>
+          <t>c9624936-845e-4011-81aa-9c96abbfe415</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="8" t="inlineStr">
@@ -40118,6 +40187,11 @@
       <c r="O537" s="8" t="n">
         <v>102679</v>
       </c>
+      <c r="P537" s="8" t="inlineStr">
+        <is>
+          <t>1303a283-e0e9-4b15-a4ab-b5a45289cb1c</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="8" t="inlineStr">
@@ -40770,6 +40844,11 @@
       <c r="O546" s="8" t="n">
         <v>120219</v>
       </c>
+      <c r="P546" s="8" t="inlineStr">
+        <is>
+          <t>a4eef40f-20bd-4dc7-8f60-bbdc3988028c</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="8" t="inlineStr">
@@ -43164,6 +43243,11 @@
       <c r="O579" s="8" t="n">
         <v>51334</v>
       </c>
+      <c r="P579" s="8" t="inlineStr">
+        <is>
+          <t>bf62340d-f322-4ca5-a11d-ebd6aaebaf3f</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="8" t="inlineStr">
@@ -43889,6 +43973,11 @@
       <c r="O589" s="8" t="n">
         <v>10297</v>
       </c>
+      <c r="P589" s="8" t="inlineStr">
+        <is>
+          <t>3e237fef-b1bb-41fc-8c0c-8a7ae5f67f68</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="8" t="inlineStr">
@@ -45115,6 +45204,11 @@
       <c r="O606" s="8" t="n">
         <v>94313</v>
       </c>
+      <c r="P606" s="8" t="inlineStr">
+        <is>
+          <t>f6e47f3e-5401-42a6-84b6-12ceca15f3c4</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="8" t="inlineStr">
@@ -45261,6 +45355,11 @@
       <c r="O608" s="8" t="n">
         <v>94368</v>
       </c>
+      <c r="P608" s="8" t="inlineStr">
+        <is>
+          <t>ef6fc148-53e1-4da4-b6d4-3b70057c8e85</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="8" t="inlineStr">
@@ -47208,6 +47307,11 @@
       <c r="O635" s="8" t="n">
         <v>146244</v>
       </c>
+      <c r="P635" s="8" t="inlineStr">
+        <is>
+          <t>86c052ee-5f8f-484c-bfd3-2a5d286c785b</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="8" t="inlineStr">
@@ -48079,6 +48183,11 @@
       <c r="O647" s="8" t="n">
         <v>144136</v>
       </c>
+      <c r="P647" s="8" t="inlineStr">
+        <is>
+          <t>cb50d426-7182-4423-bd82-a7a04f12ed76</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="8" t="inlineStr">
@@ -50820,6 +50929,11 @@
       <c r="O685" s="8" t="n">
         <v>171824</v>
       </c>
+      <c r="P685" s="8" t="inlineStr">
+        <is>
+          <t>28a2f822-fa85-4a00-a6f2-0b0d7bcde9f7</t>
+        </is>
+      </c>
       <c r="Q685" t="inlineStr">
         <is>
           <t>75f46745-77dc-4f25-83bc-e00335fb8bd9</t>
@@ -51391,6 +51505,11 @@
       <c r="O693" s="8" t="n">
         <v>128182</v>
       </c>
+      <c r="P693" s="8" t="inlineStr">
+        <is>
+          <t>50e5adbf-8f45-4613-bbc4-918083089352</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="8" t="inlineStr">
@@ -51464,6 +51583,11 @@
       <c r="O694" s="8" t="n">
         <v>162410</v>
       </c>
+      <c r="P694" s="8" t="inlineStr">
+        <is>
+          <t>9cd4f1b7-ae7a-4e07-987c-2675876f2a5c</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" s="8" t="inlineStr">
@@ -51537,6 +51661,11 @@
       <c r="O695" s="8" t="n">
         <v>90849</v>
       </c>
+      <c r="P695" s="8" t="inlineStr">
+        <is>
+          <t>075a0e97-22ad-4e79-b0f0-b51522243ed9</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="8" t="inlineStr">
@@ -51980,6 +52109,11 @@
       <c r="O701" s="8" t="n">
         <v>166388</v>
       </c>
+      <c r="P701" s="8" t="inlineStr">
+        <is>
+          <t>0a6b4be5-b43b-45f8-91d5-ca9df1892921</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="8" t="inlineStr">
@@ -53286,6 +53420,11 @@
       <c r="O719" s="8" t="n">
         <v>135838</v>
       </c>
+      <c r="P719" s="8" t="inlineStr">
+        <is>
+          <t>4d7dc8cf-dac0-48c3-a7ac-ac654bc31148</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" s="8" t="inlineStr">
@@ -53502,6 +53641,11 @@
       <c r="O722" s="8" t="n">
         <v>172180</v>
       </c>
+      <c r="P722" s="8" t="inlineStr">
+        <is>
+          <t>dfafa78c-500f-482e-b66d-d948b85a05fc</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" s="8" t="inlineStr">
@@ -53998,6 +54142,11 @@
       <c r="O729" s="8" t="n">
         <v>54847</v>
       </c>
+      <c r="P729" s="8" t="inlineStr">
+        <is>
+          <t>a04abf9c-e8e0-4dc9-a6a3-d563ef6eff88</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="8" t="inlineStr">
@@ -54942,6 +55091,11 @@
       <c r="O742" s="8" t="n">
         <v>150709</v>
       </c>
+      <c r="P742" s="8" t="inlineStr">
+        <is>
+          <t>f38466e1-4b7d-4bf4-8718-a42d52293628</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" s="8" t="inlineStr">
@@ -55015,6 +55169,9 @@
       <c r="O743" s="8" t="n">
         <v>367</v>
       </c>
+      <c r="P743" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="8" t="inlineStr">
@@ -55812,6 +55969,11 @@
       <c r="O754" s="8" t="n">
         <v>179238</v>
       </c>
+      <c r="P754" s="8" t="inlineStr">
+        <is>
+          <t>11d9fd52-df2c-41cd-988d-2862b30e0a41</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="8" t="inlineStr">
@@ -55885,6 +56047,11 @@
       <c r="O755" s="8" t="n">
         <v>189888</v>
       </c>
+      <c r="P755" s="8" t="inlineStr">
+        <is>
+          <t>192a4a38-71f9-4e20-9e07-9d0736941ca2</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" s="8" t="inlineStr">
@@ -56028,6 +56195,11 @@
       <c r="O757" s="8" t="n">
         <v>179299</v>
       </c>
+      <c r="P757" s="8" t="inlineStr">
+        <is>
+          <t>8cc3789a-4908-4be1-997f-46caec61a875</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="8" t="inlineStr">
@@ -56898,6 +57070,9 @@
           <t>Нет</t>
         </is>
       </c>
+      <c r="O769" t="n">
+        <v>108648</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770" s="8" t="inlineStr">
@@ -57185,6 +57360,11 @@
       <c r="O773" s="8" t="n">
         <v>184545</v>
       </c>
+      <c r="P773" s="8" t="inlineStr">
+        <is>
+          <t>7f5a9a49-5777-48f8-814f-ee0b8c339033</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" s="8" t="inlineStr">
@@ -58841,6 +59021,11 @@
       <c r="O796" s="8" t="n">
         <v>179152</v>
       </c>
+      <c r="P796" s="8" t="inlineStr">
+        <is>
+          <t>438f9129-d0bb-4fc1-b0bc-5d7611947b26</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" s="8" t="inlineStr">
@@ -59561,6 +59746,11 @@
       <c r="O806" s="8" t="n">
         <v>192319</v>
       </c>
+      <c r="P806" s="8" t="inlineStr">
+        <is>
+          <t>828a8c15-4f3a-4b87-9e0d-7e3f14fb30d7</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" s="8" t="inlineStr">
@@ -59707,6 +59897,11 @@
       <c r="O808" s="8" t="n">
         <v>151274</v>
       </c>
+      <c r="P808" s="8" t="inlineStr">
+        <is>
+          <t>eeb6502b-dbe7-4a83-9d1d-33b7e6f00067</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" s="8" t="inlineStr">
@@ -59780,6 +59975,11 @@
       <c r="O809" s="8" t="n">
         <v>192661</v>
       </c>
+      <c r="P809" s="8" t="inlineStr">
+        <is>
+          <t>87077ab0-0f7e-457c-bbcc-dd0a2f91d092</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" s="8" t="inlineStr">
@@ -60865,6 +61065,11 @@
       <c r="O824" s="8" t="n">
         <v>193448</v>
       </c>
+      <c r="P824" s="8" t="inlineStr">
+        <is>
+          <t>08c82ae1-8721-49a8-b0a0-71daafe162b6</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" s="8" t="inlineStr">
@@ -61147,6 +61352,11 @@
       <c r="O828" s="8" t="n">
         <v>205539</v>
       </c>
+      <c r="P828" s="8" t="inlineStr">
+        <is>
+          <t>2be5394a-1a03-4ce6-93f2-c533e10f3b3b</t>
+        </is>
+      </c>
     </row>
     <row r="829">
       <c r="A829" s="8" t="inlineStr">
@@ -61220,6 +61430,11 @@
       <c r="O829" s="8" t="n">
         <v>255165</v>
       </c>
+      <c r="P829" s="8" t="inlineStr">
+        <is>
+          <t>4f752f68-5751-4f66-b7ab-0b13cd8bf138</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" s="8" t="inlineStr">
@@ -61799,6 +62014,11 @@
       <c r="O837" s="8" t="n">
         <v>186321</v>
       </c>
+      <c r="P837" s="8" t="inlineStr">
+        <is>
+          <t>3f02ea3b-43d5-4d26-a176-44cde41c8d03</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" s="8" t="inlineStr">
@@ -62164,6 +62384,11 @@
       <c r="O842" s="8" t="n">
         <v>170172</v>
       </c>
+      <c r="P842" s="8" t="inlineStr">
+        <is>
+          <t>ec7f3649-2cae-4daa-8030-08808c0d76cd</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" s="8" t="inlineStr">
@@ -62456,6 +62681,11 @@
       <c r="O846" s="8" t="n">
         <v>193735</v>
       </c>
+      <c r="P846" s="8" t="inlineStr">
+        <is>
+          <t>6b65cde6-5b1e-4385-a380-cb6cd4e7ca41</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" s="8" t="inlineStr">
@@ -63108,6 +63338,11 @@
       <c r="O855" s="8" t="n">
         <v>39892</v>
       </c>
+      <c r="P855" s="8" t="inlineStr">
+        <is>
+          <t>c26bc65e-0250-4bcb-b38e-5f77ff09d54a</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" s="8" t="inlineStr">
@@ -63395,6 +63630,11 @@
       <c r="O859" s="8" t="n">
         <v>210386</v>
       </c>
+      <c r="P859" s="8" t="inlineStr">
+        <is>
+          <t>cadfe5c7-c10e-4982-9058-37d38e859ea4</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" s="8" t="inlineStr">
@@ -63828,6 +64068,11 @@
       <c r="O865" s="8" t="n">
         <v>211112</v>
       </c>
+      <c r="P865" s="8" t="inlineStr">
+        <is>
+          <t>8b27b453-f4f8-49e6-af0a-87af64330256</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" s="8" t="inlineStr">
@@ -63901,6 +64146,11 @@
       <c r="O866" s="8" t="n">
         <v>204759</v>
       </c>
+      <c r="P866" s="8" t="inlineStr">
+        <is>
+          <t>78487d2f-fb2c-4afd-a3bb-eafa9bd1fa32</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" s="8" t="inlineStr">
@@ -63974,6 +64224,11 @@
       <c r="O867" s="8" t="n">
         <v>221868</v>
       </c>
+      <c r="P867" s="8" t="inlineStr">
+        <is>
+          <t>5c80a97b-2d6b-49ca-b9dc-9710e8f7c98b</t>
+        </is>
+      </c>
       <c r="Q867" t="inlineStr">
         <is>
           <t>96ad6056-927f-40d5-9ad3-091441a77a22</t>
@@ -64052,6 +64307,11 @@
       <c r="O868" s="8" t="n">
         <v>212504</v>
       </c>
+      <c r="P868" s="8" t="inlineStr">
+        <is>
+          <t>39f66a49-96ed-4048-bea4-006f8eef17bd</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" s="8" t="inlineStr">
@@ -64344,6 +64604,11 @@
       <c r="O872" s="8" t="n">
         <v>214701</v>
       </c>
+      <c r="P872" s="8" t="inlineStr">
+        <is>
+          <t>f8b8d769-2b59-4e2c-909f-f178a27e7701</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" s="8" t="inlineStr">
@@ -64485,6 +64750,11 @@
       <c r="O874" s="8" t="n">
         <v>212158</v>
       </c>
+      <c r="P874" s="8" t="inlineStr">
+        <is>
+          <t>f5fa81da-f394-4af3-ac2f-07fe78191ca0</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" s="8" t="inlineStr">
@@ -65142,6 +65412,11 @@
       <c r="O883" s="8" t="n">
         <v>217230</v>
       </c>
+      <c r="P883" s="8" t="inlineStr">
+        <is>
+          <t>8ed9458e-cbdf-4022-a3d8-8ddbc948de71</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" s="8" t="inlineStr">
@@ -65355,6 +65630,11 @@
       <c r="O886" s="8" t="n">
         <v>217793</v>
       </c>
+      <c r="P886" s="8" t="inlineStr">
+        <is>
+          <t>908a41c0-6773-4446-9cf4-b07af42c9fa4</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" s="8" t="inlineStr">
@@ -65858,6 +66138,11 @@
       <c r="O893" s="8" t="n">
         <v>219439</v>
       </c>
+      <c r="P893" s="8" t="inlineStr">
+        <is>
+          <t>05ac9a2c-38f9-43b6-9b10-70e82ef98fc3</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" s="8" t="inlineStr">
@@ -66004,6 +66289,11 @@
       <c r="O895" s="8" t="n">
         <v>219468</v>
       </c>
+      <c r="P895" s="8" t="inlineStr">
+        <is>
+          <t>3e982a69-0bf4-41c4-bc62-c6645738eaf7</t>
+        </is>
+      </c>
     </row>
     <row r="896">
       <c r="A896" s="8" t="inlineStr">
@@ -67376,6 +67666,11 @@
       <c r="O914" s="8" t="n">
         <v>5374</v>
       </c>
+      <c r="P914" s="8" t="inlineStr">
+        <is>
+          <t>9bfae639-77db-4398-b8ea-bfcbac5e5f06</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" s="8" t="inlineStr">
@@ -67937,6 +68232,11 @@
       <c r="O922" s="8" t="n">
         <v>210332</v>
       </c>
+      <c r="P922" s="8" t="inlineStr">
+        <is>
+          <t>b1727556-1217-4239-90c7-97b92fb48c7a</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" s="8" t="inlineStr">
@@ -68370,6 +68670,11 @@
       <c r="O928" s="8" t="n">
         <v>225560</v>
       </c>
+      <c r="P928" s="8" t="inlineStr">
+        <is>
+          <t>70635fa2-b095-4b68-9bf0-e9fe733ab9ab</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" s="8" t="inlineStr">
@@ -68868,6 +69173,11 @@
       <c r="O935" s="8" t="n">
         <v>220152</v>
       </c>
+      <c r="P935" s="8" t="inlineStr">
+        <is>
+          <t>858226c7-68bd-4e1b-a603-384d45b88304</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" s="8" t="inlineStr">
@@ -68941,6 +69251,11 @@
       <c r="O936" s="8" t="n">
         <v>229403</v>
       </c>
+      <c r="P936" s="8" t="inlineStr">
+        <is>
+          <t>288b9f5e-d8fe-4f75-81bf-9827a9e4b009</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" s="8" t="inlineStr">
@@ -69296,6 +69611,11 @@
       <c r="O941" s="8" t="n">
         <v>175975</v>
       </c>
+      <c r="P941" s="8" t="inlineStr">
+        <is>
+          <t>056ba496-2bd3-4b56-b200-d9cb63ac48fe</t>
+        </is>
+      </c>
     </row>
     <row r="942">
       <c r="A942" s="8" t="inlineStr">
@@ -69575,6 +69895,11 @@
       <c r="O945" s="8" t="n">
         <v>219445</v>
       </c>
+      <c r="P945" s="8" t="inlineStr">
+        <is>
+          <t>46fa59b2-2847-41b1-b0e8-d5a27c44cf1a</t>
+        </is>
+      </c>
     </row>
     <row r="946">
       <c r="A946" s="8" t="inlineStr">
@@ -69643,6 +69968,11 @@
       <c r="O946" s="8" t="n">
         <v>158315</v>
       </c>
+      <c r="P946" s="8" t="inlineStr">
+        <is>
+          <t>f6f7802d-17a0-4151-b03c-6b904c8a51c6</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" s="8" t="inlineStr">
@@ -69935,6 +70265,11 @@
       <c r="O950" s="8" t="n">
         <v>230588</v>
       </c>
+      <c r="P950" s="8" t="inlineStr">
+        <is>
+          <t>cdf97eb5-c068-4479-a008-15a97b490d12</t>
+        </is>
+      </c>
     </row>
     <row r="951">
       <c r="A951" s="8" t="inlineStr">
@@ -70008,6 +70343,11 @@
       <c r="O951" s="8" t="n">
         <v>230479</v>
       </c>
+      <c r="P951" s="8" t="inlineStr">
+        <is>
+          <t>53c5f1e4-0d29-458d-ade1-dddd8ed2efb8</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" s="8" t="inlineStr">
@@ -70081,6 +70421,11 @@
       <c r="O952" s="8" t="n">
         <v>230348</v>
       </c>
+      <c r="P952" s="8" t="inlineStr">
+        <is>
+          <t>691af6d8-e534-4fee-831a-362e7629b9d8</t>
+        </is>
+      </c>
     </row>
     <row r="953">
       <c r="A953" s="8" t="inlineStr">
@@ -70514,6 +70859,11 @@
       <c r="O958" s="8" t="n">
         <v>231918</v>
       </c>
+      <c r="P958" s="8" t="inlineStr">
+        <is>
+          <t>44ee1db5-f258-49ef-a615-57342f55d3b3</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" s="8" t="inlineStr">
@@ -70874,6 +71224,11 @@
       <c r="O963" s="8" t="n">
         <v>233384</v>
       </c>
+      <c r="P963" s="8" t="inlineStr">
+        <is>
+          <t>06847978-30b3-44cd-85ff-fc0df33fd8ec</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" s="8" t="inlineStr">
@@ -70947,6 +71302,11 @@
       <c r="O964" s="8" t="n">
         <v>235916</v>
       </c>
+      <c r="P964" s="8" t="inlineStr">
+        <is>
+          <t>9dc025db-55a0-460e-9501-da35e53d3f38</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" s="8" t="inlineStr">
@@ -71020,6 +71380,11 @@
       <c r="O965" s="8" t="n">
         <v>208493</v>
       </c>
+      <c r="P965" s="8" t="inlineStr">
+        <is>
+          <t>83670562-d3fb-486b-af51-5a2377571eba</t>
+        </is>
+      </c>
     </row>
     <row r="966">
       <c r="A966" s="8" t="inlineStr">
@@ -71385,6 +71750,11 @@
       <c r="O970" s="8" t="n">
         <v>221229</v>
       </c>
+      <c r="P970" s="8" t="inlineStr">
+        <is>
+          <t>0fd8d7b9-4b06-4053-942c-dba68631ae79</t>
+        </is>
+      </c>
     </row>
     <row r="971">
       <c r="A971" s="8" t="inlineStr">
@@ -71677,6 +72047,11 @@
       <c r="O974" s="8" t="n">
         <v>228205</v>
       </c>
+      <c r="P974" s="8" t="inlineStr">
+        <is>
+          <t>24f8088d-5da2-4dc8-ad97-b98048573cd3</t>
+        </is>
+      </c>
     </row>
     <row r="975">
       <c r="A975" s="8" t="inlineStr">
@@ -71896,6 +72271,11 @@
       <c r="O977" s="8" t="n">
         <v>8199</v>
       </c>
+      <c r="P977" s="8" t="inlineStr">
+        <is>
+          <t>f6145d54-9cde-4db7-8412-523e8e2fe06a</t>
+        </is>
+      </c>
     </row>
     <row r="978">
       <c r="A978" s="8" t="inlineStr">
@@ -72256,6 +72636,11 @@
       <c r="O982" s="8" t="n">
         <v>236329</v>
       </c>
+      <c r="P982" s="8" t="inlineStr">
+        <is>
+          <t>2461f4f3-57e9-4dec-8e57-5cc1d572d10b</t>
+        </is>
+      </c>
     </row>
     <row r="983">
       <c r="A983" s="8" t="inlineStr">
@@ -72908,6 +73293,11 @@
       <c r="O991" s="8" t="n">
         <v>237555</v>
       </c>
+      <c r="P991" s="8" t="inlineStr">
+        <is>
+          <t>b4a7f98a-75d5-4412-b4b2-7eb6de216889</t>
+        </is>
+      </c>
     </row>
     <row r="992">
       <c r="A992" s="8" t="inlineStr">
@@ -73482,6 +73872,11 @@
       <c r="O999" s="8" t="n">
         <v>209124</v>
       </c>
+      <c r="P999" s="8" t="inlineStr">
+        <is>
+          <t>1a3e651c-8a79-412c-a9e7-7a7c36ab5944</t>
+        </is>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" s="8" t="inlineStr">
@@ -73701,6 +74096,11 @@
       <c r="O1002" s="8" t="n">
         <v>218278</v>
       </c>
+      <c r="P1002" s="8" t="inlineStr">
+        <is>
+          <t>2e663c9f-2ca0-494b-a5e4-6378a2016618</t>
+        </is>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" s="8" t="inlineStr">
@@ -74134,6 +74534,11 @@
       <c r="O1008" s="8" t="n">
         <v>209121</v>
       </c>
+      <c r="P1008" s="8" t="inlineStr">
+        <is>
+          <t>ceffbbe8-59f5-4b3b-bda2-43895b086f8f</t>
+        </is>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" s="8" t="inlineStr">
@@ -74499,6 +74904,11 @@
       <c r="O1013" s="8" t="n">
         <v>239450</v>
       </c>
+      <c r="P1013" s="8" t="inlineStr">
+        <is>
+          <t>aea27636-802f-49b3-81dd-021e9c8c1ae2</t>
+        </is>
+      </c>
     </row>
     <row r="1014">
       <c r="A1014" s="8" t="inlineStr">
@@ -74713,6 +75123,11 @@
       <c r="O1016" s="8" t="n">
         <v>233387</v>
       </c>
+      <c r="P1016" s="8" t="inlineStr">
+        <is>
+          <t>f39bfc9d-58d4-4eca-a4fa-9ed128a73694</t>
+        </is>
+      </c>
     </row>
     <row r="1017">
       <c r="A1017" s="8" t="inlineStr">
@@ -75297,6 +75712,11 @@
       <c r="O1024" s="8" t="n">
         <v>210343</v>
       </c>
+      <c r="P1024" s="8" t="inlineStr">
+        <is>
+          <t>fa5e7578-b4ff-4531-a711-78cd5726c636</t>
+        </is>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" s="8" t="inlineStr">
@@ -75370,6 +75790,11 @@
       <c r="O1025" s="8" t="n">
         <v>231254</v>
       </c>
+      <c r="P1025" s="8" t="inlineStr">
+        <is>
+          <t>3c7987dc-8c86-422c-bd8b-430d31cb9918</t>
+        </is>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" s="8" t="inlineStr">
@@ -75516,6 +75941,11 @@
       <c r="O1027" s="8" t="n">
         <v>241157</v>
       </c>
+      <c r="P1027" s="8" t="inlineStr">
+        <is>
+          <t>5b69debe-d5c9-4e6f-9b87-2103411ea585</t>
+        </is>
+      </c>
     </row>
     <row r="1028">
       <c r="A1028" s="8" t="inlineStr">
@@ -75657,6 +76087,11 @@
       <c r="O1029" s="8" t="n">
         <v>494</v>
       </c>
+      <c r="P1029" s="8" t="inlineStr">
+        <is>
+          <t>9d10e3cc-d118-4f8b-96f0-1dabf766a96e</t>
+        </is>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" s="8" t="inlineStr">
@@ -75725,6 +76160,11 @@
       <c r="O1030" s="8" t="n">
         <v>5397</v>
       </c>
+      <c r="P1030" s="8" t="inlineStr">
+        <is>
+          <t>a9298d0d-c22f-44da-9e6a-fa4614cb3a6c</t>
+        </is>
+      </c>
     </row>
     <row r="1031">
       <c r="A1031" s="8" t="inlineStr">
@@ -76095,6 +76535,11 @@
       <c r="O1035" s="8" t="n">
         <v>237052</v>
       </c>
+      <c r="P1035" s="8" t="inlineStr">
+        <is>
+          <t>4fca5174-5960-4d29-928b-ca37760b4d8d</t>
+        </is>
+      </c>
     </row>
     <row r="1036">
       <c r="A1036" s="8" t="inlineStr">
@@ -76241,6 +76686,11 @@
       <c r="O1037" s="8" t="n">
         <v>222364</v>
       </c>
+      <c r="P1037" s="8" t="inlineStr">
+        <is>
+          <t>446592ed-66b3-4a65-8f0b-43c55b532023</t>
+        </is>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" s="8" t="inlineStr">
@@ -77323,6 +77773,11 @@
       <c r="O1052" s="8" t="n">
         <v>25780</v>
       </c>
+      <c r="P1052" s="8" t="inlineStr">
+        <is>
+          <t>9044e405-e1ad-4935-b15b-0ff1cf610924</t>
+        </is>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" s="8" t="inlineStr">
@@ -77688,6 +78143,11 @@
       <c r="O1057" s="8" t="n">
         <v>245955</v>
       </c>
+      <c r="P1057" s="8" t="inlineStr">
+        <is>
+          <t>941659f1-62a6-4cb2-bd51-9e31aadce0bb</t>
+        </is>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" s="8" t="inlineStr">
@@ -77902,6 +78362,11 @@
       <c r="O1060" s="8" t="n">
         <v>248845</v>
       </c>
+      <c r="P1060" s="8" t="inlineStr">
+        <is>
+          <t>a11a75be-eee8-40fa-a27d-92ea1096a7d4</t>
+        </is>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" s="8" t="inlineStr">
@@ -78189,6 +78654,11 @@
       <c r="O1064" s="8" t="n">
         <v>203737</v>
       </c>
+      <c r="P1064" s="8" t="inlineStr">
+        <is>
+          <t>bc5b76c4-3bd4-4c39-89bc-2e7f1b738e38</t>
+        </is>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" s="8" t="inlineStr">
@@ -78257,6 +78727,11 @@
       <c r="O1065" s="8" t="n">
         <v>248902</v>
       </c>
+      <c r="P1065" s="8" t="inlineStr">
+        <is>
+          <t>873a0fae-149b-4745-959e-f0eac159871f</t>
+        </is>
+      </c>
     </row>
     <row r="1066">
       <c r="A1066" s="8" t="inlineStr">
@@ -78549,6 +79024,11 @@
       <c r="O1069" s="8" t="n">
         <v>248994</v>
       </c>
+      <c r="P1069" s="8" t="inlineStr">
+        <is>
+          <t>8c4f4b19-ae5c-4b6b-b619-09306ac6ee9a</t>
+        </is>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" s="8" t="inlineStr">
@@ -78835,6 +79315,11 @@
       <c r="O1073" s="8" t="n">
         <v>253128</v>
       </c>
+      <c r="P1073" s="8" t="inlineStr">
+        <is>
+          <t>283fd922-5042-42e7-94e1-29a471767167</t>
+        </is>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" s="8" t="inlineStr">
@@ -79124,6 +79609,11 @@
       <c r="O1077" s="8" t="n">
         <v>218294</v>
       </c>
+      <c r="P1077" s="8" t="inlineStr">
+        <is>
+          <t>ad64d902-7269-4ca0-896e-9bf73ebfdea9</t>
+        </is>
+      </c>
     </row>
     <row r="1078">
       <c r="A1078" s="8" t="inlineStr">
@@ -79557,6 +80047,11 @@
       <c r="O1083" s="8" t="n">
         <v>243561</v>
       </c>
+      <c r="P1083" s="8" t="inlineStr">
+        <is>
+          <t>57d2235e-cb58-4a38-88f2-dcc08e29c2ec</t>
+        </is>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" s="8" t="inlineStr">
@@ -79995,6 +80490,11 @@
       <c r="O1089" s="8" t="n">
         <v>206327</v>
       </c>
+      <c r="P1089" s="8" t="inlineStr">
+        <is>
+          <t>1ee3e417-6ad0-4e4f-b655-8cb043d07b10</t>
+        </is>
+      </c>
     </row>
     <row r="1090">
       <c r="A1090" s="8" t="inlineStr">
@@ -80584,6 +81084,11 @@
       <c r="O1097" s="8" t="n">
         <v>249641</v>
       </c>
+      <c r="P1097" s="8" t="inlineStr">
+        <is>
+          <t>aa87361d-0004-485c-8409-aa83aae13c1b</t>
+        </is>
+      </c>
     </row>
     <row r="1098">
       <c r="A1098" s="8" t="inlineStr">
@@ -81027,6 +81532,11 @@
       <c r="O1103" s="8" t="n">
         <v>255160</v>
       </c>
+      <c r="P1103" s="8" t="inlineStr">
+        <is>
+          <t>05a68060-542f-4911-86d6-946d13b74c1b</t>
+        </is>
+      </c>
     </row>
     <row r="1104">
       <c r="A1104" s="8" t="inlineStr">
@@ -81100,6 +81610,11 @@
       <c r="O1104" s="8" t="n">
         <v>255051</v>
       </c>
+      <c r="P1104" s="8" t="inlineStr">
+        <is>
+          <t>3d5d25a1-33a4-461d-bdac-f184532479e5</t>
+        </is>
+      </c>
     </row>
     <row r="1105">
       <c r="A1105" s="8" t="inlineStr">
@@ -81319,6 +81834,11 @@
       <c r="O1107" s="8" t="n">
         <v>218745</v>
       </c>
+      <c r="P1107" s="8" t="inlineStr">
+        <is>
+          <t>24028d5a-7ea2-43bf-97cc-96aa116a877c</t>
+        </is>
+      </c>
     </row>
     <row r="1108">
       <c r="A1108" s="8" t="inlineStr">
@@ -81465,6 +81985,11 @@
       <c r="O1109" s="8" t="n">
         <v>254536</v>
       </c>
+      <c r="P1109" s="8" t="inlineStr">
+        <is>
+          <t>08149e5a-b5fa-4555-9fae-a6bc45779b0b</t>
+        </is>
+      </c>
     </row>
     <row r="1110">
       <c r="A1110" s="8" t="inlineStr">
@@ -81611,6 +82136,11 @@
       <c r="O1111" s="8" t="n">
         <v>251894</v>
       </c>
+      <c r="P1111" s="8" t="inlineStr">
+        <is>
+          <t>a75b98e4-39d8-4c2c-a6a6-2a24f8aa442a</t>
+        </is>
+      </c>
     </row>
     <row r="1112">
       <c r="A1112" s="8" t="inlineStr">
@@ -81830,6 +82360,11 @@
       <c r="O1114" s="8" t="n">
         <v>256115</v>
       </c>
+      <c r="P1114" s="8" t="inlineStr">
+        <is>
+          <t>cf780473-f34e-4621-9748-d9006b0a86fe</t>
+        </is>
+      </c>
     </row>
     <row r="1115">
       <c r="A1115" s="8" t="inlineStr">
@@ -82336,6 +82871,11 @@
       <c r="O1121" s="8" t="n">
         <v>258043</v>
       </c>
+      <c r="P1121" s="8" t="inlineStr">
+        <is>
+          <t>d2b35341-2850-445e-a9c7-a42b1b6d06e9</t>
+        </is>
+      </c>
     </row>
     <row r="1122">
       <c r="A1122" s="8" t="inlineStr">
@@ -82701,6 +83241,11 @@
       <c r="O1126" s="8" t="n">
         <v>258587</v>
       </c>
+      <c r="P1126" s="8" t="inlineStr">
+        <is>
+          <t>2efec2d0-8d4b-419f-824f-4303d5722815</t>
+        </is>
+      </c>
     </row>
     <row r="1127">
       <c r="A1127" s="8" t="inlineStr">
@@ -82920,6 +83465,11 @@
       <c r="O1129" s="8" t="n">
         <v>218294</v>
       </c>
+      <c r="P1129" s="8" t="inlineStr">
+        <is>
+          <t>ad64d902-7269-4ca0-896e-9bf73ebfdea9</t>
+        </is>
+      </c>
     </row>
     <row r="1130">
       <c r="A1130" s="8" t="inlineStr">
@@ -82993,6 +83543,11 @@
       <c r="O1130" s="8" t="n">
         <v>193465</v>
       </c>
+      <c r="P1130" s="8" t="inlineStr">
+        <is>
+          <t>3f73dd0e-2adc-4546-8d40-0b5ec78ebf01</t>
+        </is>
+      </c>
     </row>
     <row r="1131">
       <c r="A1131" s="8" t="inlineStr">
@@ -83504,6 +84059,11 @@
       <c r="O1137" s="8" t="n">
         <v>222029</v>
       </c>
+      <c r="P1137" s="8" t="inlineStr">
+        <is>
+          <t>a85f6719-5fad-421a-b7ba-9c99e985cbf9</t>
+        </is>
+      </c>
     </row>
     <row r="1138">
       <c r="A1138" s="8" t="inlineStr">
@@ -83577,6 +84137,11 @@
       <c r="O1138" s="8" t="n">
         <v>259194</v>
       </c>
+      <c r="P1138" s="8" t="inlineStr">
+        <is>
+          <t>7be46ebb-9118-4ec3-9a98-34835818617f</t>
+        </is>
+      </c>
     </row>
     <row r="1139">
       <c r="A1139" s="8" t="inlineStr">
@@ -84876,6 +85441,11 @@
       <c r="O1156" s="8" t="n">
         <v>260957</v>
       </c>
+      <c r="P1156" s="8" t="inlineStr">
+        <is>
+          <t>63df4369-74d3-482f-be06-3250fa6ac558</t>
+        </is>
+      </c>
     </row>
     <row r="1157">
       <c r="A1157" s="8" t="inlineStr">
@@ -84949,6 +85519,11 @@
       <c r="O1157" s="8" t="n">
         <v>261672</v>
       </c>
+      <c r="P1157" s="8" t="inlineStr">
+        <is>
+          <t>767bdd97-ea62-4d90-b50a-2d9e1ad0c8c8</t>
+        </is>
+      </c>
     </row>
     <row r="1158">
       <c r="A1158" s="8" t="inlineStr">
@@ -85387,6 +85962,11 @@
       <c r="O1163" s="8" t="n">
         <v>261634</v>
       </c>
+      <c r="P1163" s="8" t="inlineStr">
+        <is>
+          <t>da0317af-07e4-4280-a151-3cda212211a8</t>
+        </is>
+      </c>
     </row>
     <row r="1164">
       <c r="A1164" s="8" t="inlineStr">
@@ -85822,6 +86402,14 @@
           <t>Нет</t>
         </is>
       </c>
+      <c r="O1169" t="n">
+        <v>264542</v>
+      </c>
+      <c r="P1169" s="8" t="inlineStr">
+        <is>
+          <t>f03288d8-72d6-4f26-803e-6492e4930101</t>
+        </is>
+      </c>
     </row>
     <row r="1170">
       <c r="A1170" s="8" t="inlineStr">
@@ -86114,6 +86702,11 @@
       <c r="O1173" s="8" t="n">
         <v>262712</v>
       </c>
+      <c r="P1173" s="8" t="inlineStr">
+        <is>
+          <t>d7c06136-7ac1-4a81-9418-a950601c8c31</t>
+        </is>
+      </c>
     </row>
     <row r="1174">
       <c r="A1174" s="8" t="inlineStr">
@@ -86187,6 +86780,11 @@
       <c r="O1174" s="8" t="n">
         <v>254586</v>
       </c>
+      <c r="P1174" s="8" t="inlineStr">
+        <is>
+          <t>b1289f5d-ecf9-447c-977f-912a95a3d041</t>
+        </is>
+      </c>
     </row>
     <row r="1175">
       <c r="A1175" s="8" t="inlineStr">
@@ -86406,6 +87004,11 @@
       <c r="O1177" s="8" t="n">
         <v>264073</v>
       </c>
+      <c r="P1177" s="8" t="inlineStr">
+        <is>
+          <t>f087618c-bbd6-4131-aa3e-98fb6e4621b8</t>
+        </is>
+      </c>
     </row>
     <row r="1178">
       <c r="A1178" s="8" t="inlineStr">
@@ -86768,6 +87371,11 @@
       <c r="O1182" s="8" t="n">
         <v>187307</v>
       </c>
+      <c r="P1182" s="8" t="inlineStr">
+        <is>
+          <t>7af411a9-765d-44ca-ac9f-1ea2fecc7a54</t>
+        </is>
+      </c>
     </row>
     <row r="1183">
       <c r="A1183" s="8" t="inlineStr">
@@ -87057,6 +87665,11 @@
       <c r="O1186" s="8" t="n">
         <v>2909</v>
       </c>
+      <c r="P1186" s="8" t="inlineStr">
+        <is>
+          <t>88cd7b2a-3811-4a1a-aa45-9b66fe271ae8</t>
+        </is>
+      </c>
     </row>
     <row r="1187">
       <c r="A1187" s="8" t="inlineStr">
@@ -87276,6 +87889,11 @@
       <c r="O1189" s="8" t="n">
         <v>263796</v>
       </c>
+      <c r="P1189" s="8" t="inlineStr">
+        <is>
+          <t>5f4c58c3-af1c-4915-8a9c-039d91aec476</t>
+        </is>
+      </c>
     </row>
     <row r="1190">
       <c r="A1190" s="8" t="inlineStr">
@@ -87568,6 +88186,11 @@
       <c r="O1193" s="8" t="n">
         <v>263018</v>
       </c>
+      <c r="P1193" s="8" t="inlineStr">
+        <is>
+          <t>4ec61fa0-5b44-4b31-979f-b919129a44bc</t>
+        </is>
+      </c>
     </row>
     <row r="1194">
       <c r="A1194" s="8" t="inlineStr">
@@ -87714,6 +88337,11 @@
       <c r="O1195" s="8" t="n">
         <v>182341</v>
       </c>
+      <c r="P1195" s="8" t="inlineStr">
+        <is>
+          <t>525c09ea-6ef1-4e6d-8bc6-311adfc1ae4a</t>
+        </is>
+      </c>
     </row>
     <row r="1196">
       <c r="A1196" s="8" t="inlineStr">
@@ -87787,6 +88415,11 @@
       <c r="O1196" s="8" t="n">
         <v>264604</v>
       </c>
+      <c r="P1196" s="8" t="inlineStr">
+        <is>
+          <t>07074a9f-f162-4695-a829-bf71e43caa70</t>
+        </is>
+      </c>
     </row>
     <row r="1197">
       <c r="A1197" s="8" t="inlineStr">
@@ -87860,6 +88493,11 @@
       <c r="O1197" s="8" t="n">
         <v>161154</v>
       </c>
+      <c r="P1197" s="8" t="inlineStr">
+        <is>
+          <t>51c4ce7b-cf06-4508-a4dc-324d5d50935f</t>
+        </is>
+      </c>
     </row>
     <row r="1198">
       <c r="A1198" s="8" t="inlineStr">
@@ -87933,6 +88571,11 @@
       <c r="O1198" s="8" t="n">
         <v>250384</v>
       </c>
+      <c r="P1198" s="8" t="inlineStr">
+        <is>
+          <t>9e541fb3-392b-4df2-9c51-9296846493d8</t>
+        </is>
+      </c>
     </row>
     <row r="1199">
       <c r="A1199" s="8" t="inlineStr">
@@ -88222,6 +88865,11 @@
       <c r="O1202" s="8" t="n">
         <v>265960</v>
       </c>
+      <c r="P1202" s="8" t="inlineStr">
+        <is>
+          <t>2b27c01f-bbc8-4506-a85c-3b35b7817d91</t>
+        </is>
+      </c>
     </row>
     <row r="1203">
       <c r="A1203" s="8" t="inlineStr">
@@ -88295,6 +88943,11 @@
       <c r="O1203" s="8" t="n">
         <v>218277</v>
       </c>
+      <c r="P1203" s="8" t="inlineStr">
+        <is>
+          <t>2fcb475b-6fa9-4ecd-bcdf-2f2b8e84b4ee</t>
+        </is>
+      </c>
     </row>
     <row r="1204">
       <c r="A1204" s="8" t="inlineStr">
@@ -88803,6 +89456,11 @@
       <c r="O1210" s="8" t="n">
         <v>265600</v>
       </c>
+      <c r="P1210" s="8" t="inlineStr">
+        <is>
+          <t>c4f733af-6bd0-4e3f-82a0-26fb9f1e0df6</t>
+        </is>
+      </c>
     </row>
     <row r="1211">
       <c r="A1211" s="8" t="inlineStr">
@@ -88949,6 +89607,11 @@
       <c r="O1212" s="8" t="n">
         <v>91962</v>
       </c>
+      <c r="P1212" s="8" t="inlineStr">
+        <is>
+          <t>20ad41ef-046b-4b77-8cf3-aab20d62a912</t>
+        </is>
+      </c>
     </row>
     <row r="1213">
       <c r="A1213" s="8" t="inlineStr">
@@ -89022,6 +89685,11 @@
       <c r="O1213" s="8" t="n">
         <v>265962</v>
       </c>
+      <c r="P1213" s="8" t="inlineStr">
+        <is>
+          <t>45e9f58d-84f0-4cb9-a6d6-ba40a2f90e19</t>
+        </is>
+      </c>
     </row>
     <row r="1214">
       <c r="A1214" s="8" t="inlineStr">
@@ -89095,6 +89763,11 @@
       <c r="O1214" s="8" t="n">
         <v>264847</v>
       </c>
+      <c r="P1214" s="8" t="inlineStr">
+        <is>
+          <t>79954aeb-67d9-416c-bf2c-1718b06ca9c0</t>
+        </is>
+      </c>
     </row>
     <row r="1215">
       <c r="A1215" s="8" t="inlineStr">
@@ -89241,6 +89914,11 @@
       <c r="O1216" s="8" t="n">
         <v>266218</v>
       </c>
+      <c r="P1216" s="8" t="inlineStr">
+        <is>
+          <t>5e5f5989-ab6a-4e92-a00c-3946b174bbbf</t>
+        </is>
+      </c>
     </row>
     <row r="1217">
       <c r="A1217" s="8" t="inlineStr">
@@ -89314,6 +89992,11 @@
       <c r="O1217" s="8" t="n">
         <v>267583</v>
       </c>
+      <c r="P1217" s="8" t="inlineStr">
+        <is>
+          <t>222a9996-e00b-4e79-a05c-572d2bae493b</t>
+        </is>
+      </c>
     </row>
     <row r="1218">
       <c r="A1218" s="8" t="inlineStr">
@@ -89387,6 +90070,11 @@
       <c r="O1218" s="8" t="n">
         <v>215651</v>
       </c>
+      <c r="P1218" s="8" t="inlineStr">
+        <is>
+          <t>826b9645-0dda-4775-af53-594010519df3</t>
+        </is>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" s="8" t="inlineStr">
@@ -89460,6 +90148,11 @@
       <c r="O1219" s="8" t="n">
         <v>266390</v>
       </c>
+      <c r="P1219" s="8" t="inlineStr">
+        <is>
+          <t>78083b26-fe2f-4027-b3bf-4c05a1d222eb</t>
+        </is>
+      </c>
     </row>
     <row r="1220">
       <c r="A1220" s="8" t="inlineStr">
@@ -89533,6 +90226,11 @@
       <c r="O1220" s="8" t="n">
         <v>266234</v>
       </c>
+      <c r="P1220" s="8" t="inlineStr">
+        <is>
+          <t>8287ec38-66c8-45bd-ac76-bf4de9471e7c</t>
+        </is>
+      </c>
     </row>
     <row r="1221">
       <c r="A1221" s="8" t="inlineStr">
@@ -89606,6 +90304,11 @@
       <c r="O1221" s="8" t="n">
         <v>266516</v>
       </c>
+      <c r="P1221" s="8" t="inlineStr">
+        <is>
+          <t>a8c89657-fa65-40a2-82fd-a2841a2b1365</t>
+        </is>
+      </c>
     </row>
     <row r="1222">
       <c r="A1222" s="8" t="inlineStr">
@@ -89679,6 +90382,11 @@
       <c r="O1222" s="8" t="n">
         <v>266517</v>
       </c>
+      <c r="P1222" s="8" t="inlineStr">
+        <is>
+          <t>9ffa916b-80cc-4b4c-8f08-f23a54688628</t>
+        </is>
+      </c>
     </row>
     <row r="1223">
       <c r="A1223" s="8" t="inlineStr">
@@ -89825,6 +90533,11 @@
       <c r="O1224" s="8" t="n">
         <v>266874</v>
       </c>
+      <c r="P1224" s="8" t="inlineStr">
+        <is>
+          <t>053cf348-3689-4ae5-ba4f-e53c3b0f2fae</t>
+        </is>
+      </c>
     </row>
     <row r="1225">
       <c r="A1225" s="8" t="inlineStr">
@@ -90117,6 +90830,11 @@
       <c r="O1228" s="8" t="n">
         <v>267257</v>
       </c>
+      <c r="P1228" s="8" t="inlineStr">
+        <is>
+          <t>627ce461-0072-45f1-ab56-5e7b1d25d6e9</t>
+        </is>
+      </c>
     </row>
     <row r="1229">
       <c r="A1229" s="8" t="inlineStr">
@@ -90263,6 +90981,11 @@
       <c r="O1230" s="8" t="n">
         <v>267328</v>
       </c>
+      <c r="P1230" s="8" t="inlineStr">
+        <is>
+          <t>4b6f45ac-ed9a-4f5f-83a8-4ce8ad106cad</t>
+        </is>
+      </c>
     </row>
     <row r="1231">
       <c r="A1231" s="8" t="inlineStr">
@@ -90336,6 +91059,11 @@
       <c r="O1231" s="8" t="n">
         <v>267371</v>
       </c>
+      <c r="P1231" s="8" t="inlineStr">
+        <is>
+          <t>1dae0e3b-6adc-47f6-b592-daa39910bcb8</t>
+        </is>
+      </c>
     </row>
     <row r="1232">
       <c r="A1232" s="8" t="inlineStr">
@@ -90409,6 +91137,11 @@
       <c r="O1232" s="8" t="n">
         <v>267373</v>
       </c>
+      <c r="P1232" s="8" t="inlineStr">
+        <is>
+          <t>489f064c-e7af-46e4-b99f-c32ed6a07c8a</t>
+        </is>
+      </c>
     </row>
     <row r="1233">
       <c r="A1233" s="8" t="inlineStr">
@@ -90628,6 +91361,11 @@
       <c r="O1235" s="8" t="n">
         <v>267689</v>
       </c>
+      <c r="P1235" s="8" t="inlineStr">
+        <is>
+          <t>0562eca1-6539-4afb-9af7-22ff4b28acf4</t>
+        </is>
+      </c>
     </row>
     <row r="1236">
       <c r="A1236" s="8" t="inlineStr">
@@ -90847,6 +91585,11 @@
       <c r="O1238" s="8" t="n">
         <v>132877</v>
       </c>
+      <c r="P1238" s="8" t="inlineStr">
+        <is>
+          <t>cf72662f-9ba7-474c-a870-caf07a2d8a79</t>
+        </is>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" s="8" t="inlineStr">
@@ -90917,6 +91660,14 @@
           <t>Нет</t>
         </is>
       </c>
+      <c r="O1239" t="n">
+        <v>269400</v>
+      </c>
+      <c r="P1239" s="8" t="inlineStr">
+        <is>
+          <t>4f1c5247-49af-4ae8-89ab-256eb2d1cdea</t>
+        </is>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" s="8" t="inlineStr">
@@ -91279,6 +92030,11 @@
       <c r="O1244" s="8" t="n">
         <v>268511</v>
       </c>
+      <c r="P1244" s="8" t="inlineStr">
+        <is>
+          <t>868d22a8-1549-4adc-b74f-5f86d2c83bf1</t>
+        </is>
+      </c>
     </row>
     <row r="1245">
       <c r="A1245" s="8" t="inlineStr">
@@ -91349,6 +92105,9 @@
           <t>Нет</t>
         </is>
       </c>
+      <c r="O1245" t="n">
+        <v>269293</v>
+      </c>
     </row>
     <row r="1246">
       <c r="A1246" s="8" t="inlineStr">
@@ -91422,6 +92181,11 @@
       <c r="O1246" s="8" t="n">
         <v>269074</v>
       </c>
+      <c r="P1246" s="8" t="inlineStr">
+        <is>
+          <t>50dcf553-2836-42ea-b89f-70cf88f1a5ed</t>
+        </is>
+      </c>
     </row>
     <row r="1247">
       <c r="A1247" s="8" t="inlineStr">
@@ -91927,6 +92691,14 @@
           <t>Нет</t>
         </is>
       </c>
+      <c r="O1253" t="n">
+        <v>245711</v>
+      </c>
+      <c r="P1253" s="8" t="inlineStr">
+        <is>
+          <t>d2b095eb-ab47-4ccf-8f76-ad17ba1e6780</t>
+        </is>
+      </c>
     </row>
     <row r="1254">
       <c r="A1254" s="8" t="inlineStr">
@@ -92000,6 +92772,11 @@
       <c r="O1254" s="8" t="n">
         <v>268940</v>
       </c>
+      <c r="P1254" s="8" t="inlineStr">
+        <is>
+          <t>3df85966-9c2f-40f6-a022-71590b5e926b</t>
+        </is>
+      </c>
     </row>
     <row r="1255">
       <c r="A1255" s="8" t="inlineStr">
@@ -92292,6 +93069,11 @@
       <c r="O1258" s="8" t="n">
         <v>235028</v>
       </c>
+      <c r="P1258" s="8" t="inlineStr">
+        <is>
+          <t>ee06edaf-19f1-4516-bb13-b2bba60b5494</t>
+        </is>
+      </c>
     </row>
     <row r="1259">
       <c r="A1259" s="8" t="inlineStr">
@@ -92364,6 +93146,7307 @@
       </c>
       <c r="O1259" s="8" t="n">
         <v>269098</v>
+      </c>
+      <c r="P1259" s="8" t="inlineStr">
+        <is>
+          <t>de2df83a-33a0-4c5e-8be6-a73d655bace6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="8" t="inlineStr">
+        <is>
+          <t>14/04-П</t>
+        </is>
+      </c>
+      <c r="B1260" s="8" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>ООО "РА МЕДИА ВЕЙС"</t>
+        </is>
+      </c>
+      <c r="E1260" s="8" t="inlineStr">
+        <is>
+          <t>7718873967</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>ООО «НЕО-ФАРМ»</t>
+        </is>
+      </c>
+      <c r="G1260" s="8" t="inlineStr">
+        <is>
+          <t>7732121736</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1260" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1260" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1260" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1260" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1260" t="n">
+        <v>58391</v>
+      </c>
+      <c r="P1260" s="8" t="inlineStr">
+        <is>
+          <t>ff67ce9b-949d-40a5-82b1-4ea78f9385b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="8" t="inlineStr">
+        <is>
+          <t>LA09202407100011</t>
+        </is>
+      </c>
+      <c r="B1261" s="8" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>ЗАО ИА Риалвеб</t>
+        </is>
+      </c>
+      <c r="E1261" s="8" t="inlineStr">
+        <is>
+          <t>7813323882</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1261" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1261" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1261" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M1261" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1261" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1261" t="n">
+        <v>145309</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="8" t="inlineStr">
+        <is>
+          <t>MPC-287</t>
+        </is>
+      </c>
+      <c r="B1262" s="8" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Елизавета Негуляева</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>ООО "МЕДИАПЛАН КОНСАЛТИНГ"</t>
+        </is>
+      </c>
+      <c r="E1262" s="8" t="inlineStr">
+        <is>
+          <t>7726462336</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>ООО "Юнайтед Петрокемикалс"</t>
+        </is>
+      </c>
+      <c r="G1262" s="8" t="inlineStr">
+        <is>
+          <t>4025450626</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1262" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1262" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1262" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1262" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1262" t="n">
+        <v>170914</v>
+      </c>
+      <c r="P1262" s="8" t="inlineStr">
+        <is>
+          <t>0f877957-20d1-4092-a8bd-25b0a2356eec</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="8" t="inlineStr">
+        <is>
+          <t>29063984/Р430-01/31.03.2025</t>
+        </is>
+      </c>
+      <c r="B1263" s="8" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Елизавета Негуляева</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>АО «Медиа Инстинкт»</t>
+        </is>
+      </c>
+      <c r="E1263" s="8" t="inlineStr">
+        <is>
+          <t>7714760793</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>ПАО "Аэрофлот-российские авиалинии"</t>
+        </is>
+      </c>
+      <c r="G1263" s="8" t="inlineStr">
+        <is>
+          <t>7712040126</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1263" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1263" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1263" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1263" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1263" t="n">
+        <v>214859</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="8" t="inlineStr">
+        <is>
+          <t>K-22/2015</t>
+        </is>
+      </c>
+      <c r="B1264" s="8" t="inlineStr">
+        <is>
+          <t>2015-12-21</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Надежда Рашковецкая</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>ООО "Мера Русс Медиа"</t>
+        </is>
+      </c>
+      <c r="E1264" s="8" t="inlineStr">
+        <is>
+          <t>7717707438</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>ООО "ЯНДЕКС.ТАКСИ"</t>
+        </is>
+      </c>
+      <c r="G1264" s="8" t="inlineStr">
+        <is>
+          <t>7704340310</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="J1264" s="8" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="K1264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1264" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1264" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1264" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1264" t="n">
+        <v>227484</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="8" t="inlineStr">
+        <is>
+          <t>D-10-С-21-1130</t>
+        </is>
+      </c>
+      <c r="B1265" s="8" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>ООО "ИА РиалВеб"</t>
+        </is>
+      </c>
+      <c r="E1265" s="8" t="inlineStr">
+        <is>
+          <t>7813323882</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>АО "АВИАКОМПАНИЯ "СИБИРЬ"</t>
+        </is>
+      </c>
+      <c r="G1265" s="8" t="inlineStr">
+        <is>
+          <t>5448100656</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1265" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1265" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1265" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1265" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1265" t="n">
+        <v>206250</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="8" t="inlineStr">
+        <is>
+          <t>26/12-РК</t>
+        </is>
+      </c>
+      <c r="B1266" s="8" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>ООО «Майоли Фарма»</t>
+        </is>
+      </c>
+      <c r="G1266" s="8" t="inlineStr">
+        <is>
+          <t>9709071431</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1266" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1266" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1266" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1266" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1266" t="n">
+        <v>173162</v>
+      </c>
+      <c r="P1266" s="8" t="inlineStr">
+        <is>
+          <t>684c0d5a-f824-41a7-af5f-061ca55159e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="8" t="inlineStr">
+        <is>
+          <t>№ПРАЙМ/2026/1</t>
+        </is>
+      </c>
+      <c r="B1267" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>ООО «С-МАРКЕТИНГ»</t>
+        </is>
+      </c>
+      <c r="E1267" s="8" t="inlineStr">
+        <is>
+          <t>7736319695</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>АО "ЦПЛ"</t>
+        </is>
+      </c>
+      <c r="G1267" s="8" t="inlineStr">
+        <is>
+          <t>7702770003</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1267" s="8" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="K1267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1267" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1267" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1267" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1267" t="n">
+        <v>259475</v>
+      </c>
+      <c r="P1267" s="8" t="inlineStr">
+        <is>
+          <t>e9406ea7-97bd-4c34-a97c-b0a608e0868f</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="8" t="inlineStr">
+        <is>
+          <t>ДОГ-MCM-20-1010</t>
+        </is>
+      </c>
+      <c r="B1268" s="8" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>ООО "МЕДИАСИСТЕМ"</t>
+        </is>
+      </c>
+      <c r="E1268" s="8" t="inlineStr">
+        <is>
+          <t>7731644420</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>ЗАО "АКЗО НОБЕЛЬ ДЕКОР"</t>
+        </is>
+      </c>
+      <c r="G1268" s="8" t="inlineStr">
+        <is>
+          <t>5001027607</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1268" s="8" t="inlineStr">
+        <is>
+          <t>Заключение договоров</t>
+        </is>
+      </c>
+      <c r="K1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1268" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1268" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1268" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1268" t="n">
+        <v>264956</v>
+      </c>
+      <c r="P1268" s="8" t="inlineStr">
+        <is>
+          <t>b55b5e8e-2cec-4a58-aea9-e6ea89ea2ab5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="8" t="inlineStr">
+        <is>
+          <t>ОИ-0112/25</t>
+        </is>
+      </c>
+      <c r="B1269" s="8" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>ООО "ОККАМ ИКС"</t>
+        </is>
+      </c>
+      <c r="E1269" s="8" t="inlineStr">
+        <is>
+          <t>7731596504</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>ООО "ДЖЕЙТНЛ"</t>
+        </is>
+      </c>
+      <c r="G1269" s="8" t="inlineStr">
+        <is>
+          <t>7731190470</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1269" s="8" t="inlineStr">
+        <is>
+          <t>Заключение договоров</t>
+        </is>
+      </c>
+      <c r="K1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1269" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1269" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1269" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1269" t="n">
+        <v>267653</v>
+      </c>
+      <c r="P1269" s="8" t="inlineStr">
+        <is>
+          <t>b114e9cf-6247-4610-8802-3b07ecf8c969</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="8" t="inlineStr">
+        <is>
+          <t>ДО-0105</t>
+        </is>
+      </c>
+      <c r="B1270" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>ООО "ОККАМ"</t>
+        </is>
+      </c>
+      <c r="E1270" s="8" t="inlineStr">
+        <is>
+          <t>7709909600</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>ООО "ЭСТЕО РУС"</t>
+        </is>
+      </c>
+      <c r="G1270" s="8" t="inlineStr">
+        <is>
+          <t>7743487147</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1270" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1270" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1270" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1270" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1270" t="n">
+        <v>269246</v>
+      </c>
+      <c r="P1270" s="8" t="inlineStr">
+        <is>
+          <t>b2e6143c-2611-450b-b17c-b7e9a8efba58</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="8" t="inlineStr">
+        <is>
+          <t>01062026/М</t>
+        </is>
+      </c>
+      <c r="B1271" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>ООО «Медиа 108»</t>
+        </is>
+      </c>
+      <c r="E1271" s="8" t="inlineStr">
+        <is>
+          <t>7728845285</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>ООО «СПЕЦИАЛИЗИРОВАННЫЙ ЗАСТРОЙЩИК «СЕВЕРНЫЙ ПОРТ 7»</t>
+        </is>
+      </c>
+      <c r="G1271" s="8" t="inlineStr">
+        <is>
+          <t>9717106889</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1271" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1271" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1271" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1271" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1271" t="n">
+        <v>269277</v>
+      </c>
+      <c r="P1271" s="8" t="inlineStr">
+        <is>
+          <t>56b374d8-71b6-44c3-9600-2fc3a034ab5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="8" t="inlineStr">
+        <is>
+          <t>23/2026</t>
+        </is>
+      </c>
+      <c r="B1272" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Елизавета Негуляева</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>ООО Специализированный Застройщик "Инвест Менеджмент Групп"</t>
+        </is>
+      </c>
+      <c r="E1272" s="8" t="inlineStr">
+        <is>
+          <t>7704546582</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>АО «Медиа Инстинкт»</t>
+        </is>
+      </c>
+      <c r="G1272" s="8" t="inlineStr">
+        <is>
+          <t>7714760793</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1272" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1272" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1272" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1272" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1272" t="n">
+        <v>269310</v>
+      </c>
+      <c r="P1272" s="8" t="inlineStr">
+        <is>
+          <t>e41a53cc-cdc8-4466-bed7-d572cfbb3d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="8" t="inlineStr">
+        <is>
+          <t>23052025/М</t>
+        </is>
+      </c>
+      <c r="B1273" s="8" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Анна Кочукова</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>ООО "Медиа 108"</t>
+        </is>
+      </c>
+      <c r="E1273" s="8" t="inlineStr">
+        <is>
+          <t>7728845285</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>ООО «СПЕЦИАЛИЗИРОВАННЫЙ ЗАСТРОЙЩИК «СТАВНИ ОБВОДНЫЙ»</t>
+        </is>
+      </c>
+      <c r="G1273" s="8" t="inlineStr">
+        <is>
+          <t>7840111990</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1273" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1273" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1273" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1273" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1273" t="n">
+        <v>269379</v>
+      </c>
+      <c r="P1273" s="8" t="inlineStr">
+        <is>
+          <t>ada54e0f-ab27-4b1b-bae1-149dee409f7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="8" t="inlineStr">
+        <is>
+          <t>RS-0226</t>
+        </is>
+      </c>
+      <c r="B1274" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>ООО "АДВЕЛОП"</t>
+        </is>
+      </c>
+      <c r="E1274" s="8" t="inlineStr">
+        <is>
+          <t>7725356230</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>ООО "РЕЗИДЕНС СЕРВИС"</t>
+        </is>
+      </c>
+      <c r="G1274" s="8" t="inlineStr">
+        <is>
+          <t>7730240706</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1274" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1274" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1274" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1274" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1274" t="n">
+        <v>267763</v>
+      </c>
+      <c r="P1274" s="8" t="inlineStr">
+        <is>
+          <t>e1256b83-0f6a-46df-8a85-b4c70777567d</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="8" t="inlineStr">
+        <is>
+          <t>КП-1/26</t>
+        </is>
+      </c>
+      <c r="B1275" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Anastasia Tokareva</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>ООО УК «Нектарин»</t>
+        </is>
+      </c>
+      <c r="E1275" s="8" t="inlineStr">
+        <is>
+          <t>7710703730</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>ООО "СЗ КАПЕЛЛА"</t>
+        </is>
+      </c>
+      <c r="G1275" s="8" t="inlineStr">
+        <is>
+          <t>7806589634</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1275" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1275" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1275" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1275" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1275" t="n">
+        <v>269668</v>
+      </c>
+      <c r="P1275" s="8" t="inlineStr">
+        <is>
+          <t>66372052-a567-4153-8d01-9a737f318a7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="8" t="inlineStr">
+        <is>
+          <t>0126-RPARK</t>
+        </is>
+      </c>
+      <c r="B1276" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Anastasia Tokareva</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>ООО "Юниверсал Медиа Уорлдвайд"</t>
+        </is>
+      </c>
+      <c r="E1276" s="8" t="inlineStr">
+        <is>
+          <t>7704221993</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>ООО "СПЕЦИАЛИЗИРОВАННЫЙ ЗАСТРОЙЩИК "РОДИНА ПАРК"</t>
+        </is>
+      </c>
+      <c r="G1276" s="8" t="inlineStr">
+        <is>
+          <t>7704638233</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1276" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1276" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1276" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1276" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1276" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1276" t="n">
+        <v>269756</v>
+      </c>
+      <c r="P1276" s="8" t="inlineStr">
+        <is>
+          <t>6131ea47-e490-40bf-b92a-a83ea5802db1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B1277" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Анна Кочукова</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>ООО "АДВЕЛОП"</t>
+        </is>
+      </c>
+      <c r="E1277" s="8" t="inlineStr">
+        <is>
+          <t>7725356230</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>ООО «Центр развития проектов «Петербургская Недвижимость»</t>
+        </is>
+      </c>
+      <c r="G1277" s="8" t="inlineStr">
+        <is>
+          <t>7816094750</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1277" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1277" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1277" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1277" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1277" t="n">
+        <v>269828</v>
+      </c>
+      <c r="P1277" s="8" t="inlineStr">
+        <is>
+          <t>01b167bc-2408-4de8-9fee-d1f2ff5d317f</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="8" t="inlineStr">
+        <is>
+          <t>БНО0311</t>
+        </is>
+      </c>
+      <c r="B1278" s="8" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Надежда Рашковецкая</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>АО "ПРОКСИМИТИ"</t>
+        </is>
+      </c>
+      <c r="E1278" s="8" t="inlineStr">
+        <is>
+          <t>7710586350</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>ООО "БИОНОРИКА"</t>
+        </is>
+      </c>
+      <c r="G1278" s="8" t="inlineStr">
+        <is>
+          <t>7729590470</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1278" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1278" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1278" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1278" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1278" t="n">
+        <v>248821</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="8" t="inlineStr">
+        <is>
+          <t>б/н</t>
+        </is>
+      </c>
+      <c r="B1279" s="8" t="inlineStr">
+        <is>
+          <t>2022-12-29</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Tatyana Pankova</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>ООО "МЕДИАМЭЙКЕР"</t>
+        </is>
+      </c>
+      <c r="E1279" s="8" t="inlineStr">
+        <is>
+          <t>7731529804</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>ООО "БАЙЕРСДОРФ"</t>
+        </is>
+      </c>
+      <c r="G1279" s="8" t="inlineStr">
+        <is>
+          <t>7702226629</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1279" s="8" t="inlineStr">
+        <is>
+          <t>Заключение договоров</t>
+        </is>
+      </c>
+      <c r="K1279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1279" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1279" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1279" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1279" t="n">
+        <v>269838</v>
+      </c>
+      <c r="P1279" s="8" t="inlineStr">
+        <is>
+          <t>c7753c5d-d94c-4bab-90bc-0e08280bcf17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="8" t="inlineStr">
+        <is>
+          <t>10688566/2023</t>
+        </is>
+      </c>
+      <c r="B1280" s="8" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Darina Yureva</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>ООО "Мера Русс Медиа"</t>
+        </is>
+      </c>
+      <c r="E1280" s="8" t="inlineStr">
+        <is>
+          <t>7717707438</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>ООО "Яндекс Плюс"</t>
+        </is>
+      </c>
+      <c r="G1280" s="8" t="inlineStr">
+        <is>
+          <t>9705177420</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="J1280" s="8" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="K1280" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1280" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1280" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1280" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1280" t="n">
+        <v>244155</v>
+      </c>
+      <c r="P1280" s="8" t="inlineStr">
+        <is>
+          <t>e58c25c1-8235-4656-ad93-c1ceba51a242</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="8" t="inlineStr">
+        <is>
+          <t>№4/2026/1</t>
+        </is>
+      </c>
+      <c r="B1281" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Арина Костюшина</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>ООО «Хорайзн Медиа»</t>
+        </is>
+      </c>
+      <c r="E1281" s="8" t="inlineStr">
+        <is>
+          <t>7731463631</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>ООО "СЗ "ЖК ЯРКИЙ. РИГА"</t>
+        </is>
+      </c>
+      <c r="G1281" s="8" t="inlineStr">
+        <is>
+          <t>5024214427</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1281" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1281" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1281" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1281" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1281" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1281" t="n">
+        <v>269916</v>
+      </c>
+      <c r="P1281" s="8" t="inlineStr">
+        <is>
+          <t>5cca0ca1-a576-41f7-afce-b9aae02d2a8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="8" t="inlineStr">
+        <is>
+          <t>АД/НЮ-СЗПР</t>
+        </is>
+      </c>
+      <c r="B1282" s="8" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Yulia Vydai</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>ООО "НЕГА ЮГ"</t>
+        </is>
+      </c>
+      <c r="E1282" s="8" t="inlineStr">
+        <is>
+          <t>2304051152</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>ООО "СПЕЦИАЛИЗИРОВАННЫЙ ЗАСТРОЙЩИК "ПРЕМИУМ"</t>
+        </is>
+      </c>
+      <c r="G1282" s="8" t="inlineStr">
+        <is>
+          <t>9723102794</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1282" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1282" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1282" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1282" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1282" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1282" t="n">
+        <v>270356</v>
+      </c>
+      <c r="P1282" s="8" t="inlineStr">
+        <is>
+          <t>71290f52-7f7a-4d7f-a3da-07fbf9ed269d</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="8" t="inlineStr">
+        <is>
+          <t>230901/1-DBP</t>
+        </is>
+      </c>
+      <c r="B1283" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Мария Смирнова</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>ООО "КБП"</t>
+        </is>
+      </c>
+      <c r="E1283" s="8" t="inlineStr">
+        <is>
+          <t>9725063452</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>ФОНД ДОМ.РФ</t>
+        </is>
+      </c>
+      <c r="G1283" s="8" t="inlineStr">
+        <is>
+          <t>7704370836</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="J1283" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1283" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1283" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1283" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1283" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="8" t="inlineStr">
+        <is>
+          <t>11184374</t>
+        </is>
+      </c>
+      <c r="B1284" s="8" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Darina Yureva</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>ООО "Мера Русс Медиа"</t>
+        </is>
+      </c>
+      <c r="E1284" s="8" t="inlineStr">
+        <is>
+          <t>7717707438</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>ООО "ФИНАНСОВЫЕ И ПЛАТЕЖНЫЕ ТЕХНОЛОГИИ"</t>
+        </is>
+      </c>
+      <c r="G1284" s="8" t="inlineStr">
+        <is>
+          <t>9705212635</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="J1284" s="8" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="K1284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1284" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1284" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1284" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1284" t="n">
+        <v>195628</v>
+      </c>
+      <c r="P1284" s="8" t="inlineStr">
+        <is>
+          <t>969eba96-4849-4b48-a05d-40ba752e7dcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="8" t="inlineStr">
+        <is>
+          <t>№ 29/05-РК</t>
+        </is>
+      </c>
+      <c r="B1285" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Anastasia Tokareva</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>ООО «СЛ Медиа»</t>
+        </is>
+      </c>
+      <c r="E1285" s="8" t="inlineStr">
+        <is>
+          <t>7715018344</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>АО "Л.АРГО"</t>
+        </is>
+      </c>
+      <c r="G1285" s="8" t="inlineStr">
+        <is>
+          <t>7706029903</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1285" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1285" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1285" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1285" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1285" t="n">
+        <v>271250</v>
+      </c>
+      <c r="P1285" s="8" t="inlineStr">
+        <is>
+          <t>efa5e293-796c-4a54-bfeb-5c1b5174869c</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B1286" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1286" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>АО "ЭЙЧ ЭНД ЭН"</t>
+        </is>
+      </c>
+      <c r="G1286" s="8" t="inlineStr">
+        <is>
+          <t>7714626332</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1286" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1286" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1286" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1286" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1286" t="n">
+        <v>278373</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1287" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1287" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1287" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1287" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1287" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1287" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1287" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1287" t="n">
+        <v>271724</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1288" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1288" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>ООО "ВК"</t>
+        </is>
+      </c>
+      <c r="G1288" s="8" t="inlineStr">
+        <is>
+          <t>7743001840</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1288" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1288" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1288" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1288" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q1288" s="8" t="inlineStr">
+        <is>
+          <t>d90493fb-77bc-41e7-971e-336a9b49c1ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1289" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1289" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>ООО "ВК"</t>
+        </is>
+      </c>
+      <c r="G1289" s="8" t="inlineStr">
+        <is>
+          <t>7743001840</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1289" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1289" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1289" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1289" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q1289" s="8" t="inlineStr">
+        <is>
+          <t>3d00be2f-a2dc-4515-be24-a13254e6ea23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1290" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>ООО «Звезда ЦИ»</t>
+        </is>
+      </c>
+      <c r="E1290" s="8" t="inlineStr">
+        <is>
+          <t>9709030065</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>АО «Премьер-Фарма»</t>
+        </is>
+      </c>
+      <c r="G1290" s="8" t="inlineStr">
+        <is>
+          <t>9701157101</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1290" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1290" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1290" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1290" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1290" t="n">
+        <v>271782</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1291" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>ООО «Звезда ЦИ»</t>
+        </is>
+      </c>
+      <c r="E1291" s="8" t="inlineStr">
+        <is>
+          <t>9709030065</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>АО «Премьер-Фарма»</t>
+        </is>
+      </c>
+      <c r="G1291" s="8" t="inlineStr">
+        <is>
+          <t>9701157101</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1291" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1291" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1291" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1291" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1291" t="n">
+        <v>271832</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="8" t="inlineStr">
+        <is>
+          <t>23-04-2026</t>
+        </is>
+      </c>
+      <c r="B1292" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Yulia Bezinskih</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>ООО «Метод Медиа»</t>
+        </is>
+      </c>
+      <c r="E1292" s="8" t="inlineStr">
+        <is>
+          <t>7726465288</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>ООО «Ориент Хоусхолд Апплиансес»</t>
+        </is>
+      </c>
+      <c r="G1292" s="8" t="inlineStr">
+        <is>
+          <t>7714702390</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1292" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1292" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1292" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1292" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1292" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1292" t="n">
+        <v>269124</v>
+      </c>
+      <c r="P1292" s="8" t="inlineStr">
+        <is>
+          <t>86f733b4-c444-4793-8a6b-abd128827d1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="8" t="inlineStr">
+        <is>
+          <t>203/22-5</t>
+        </is>
+      </c>
+      <c r="B1293" s="8" t="inlineStr">
+        <is>
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Anastasia Tokareva</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>ООО "ДНС Ритейл"</t>
+        </is>
+      </c>
+      <c r="E1293" s="8" t="inlineStr">
+        <is>
+          <t>2540167061</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>ООО "АЙ ЭЙЧ ПИ АППЛАЕНСЕС СЕЙЛС"</t>
+        </is>
+      </c>
+      <c r="G1293" s="8" t="inlineStr">
+        <is>
+          <t>7717654289</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1293" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1293" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1293" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1293" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1293" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1293" t="n">
+        <v>272496</v>
+      </c>
+      <c r="P1293" s="8" t="inlineStr">
+        <is>
+          <t>c80ba671-e121-46b5-a3eb-1aa64dfdcc3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="8" t="inlineStr">
+        <is>
+          <t>1|2025</t>
+        </is>
+      </c>
+      <c r="B1294" s="8" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Yulia Bezinskih</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>ООО «ГРЕЙТ ДИДЖИТАЛ М»</t>
+        </is>
+      </c>
+      <c r="E1294" s="8" t="inlineStr">
+        <is>
+          <t>7805806607</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>ООО "СПЕЦИАЛИЗИРОВАННЫЙ ЗАСТРОЙЩИК СОЮЗ ИНВЕСТ"</t>
+        </is>
+      </c>
+      <c r="G1294" s="8" t="inlineStr">
+        <is>
+          <t>7813232681</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1294" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1294" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1294" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1294" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1294" t="n">
+        <v>264438</v>
+      </c>
+      <c r="P1294" s="8" t="inlineStr">
+        <is>
+          <t>0ff2f79b-e6dd-40c2-9428-69123467228e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="8" t="inlineStr">
+        <is>
+          <t>DA010120-01</t>
+        </is>
+      </c>
+      <c r="B1295" s="8" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Елизавета Седых</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>ООО "ОККАМ ИКС"</t>
+        </is>
+      </c>
+      <c r="E1295" s="8" t="inlineStr">
+        <is>
+          <t>7731596504</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>ООО "МИЛФУДС"</t>
+        </is>
+      </c>
+      <c r="G1295" s="8" t="inlineStr">
+        <is>
+          <t>6949003920</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1295" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1295" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1295" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1295" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1295" t="n">
+        <v>272299</v>
+      </c>
+      <c r="P1295" s="8" t="inlineStr">
+        <is>
+          <t>1af43912-517e-418f-8f41-9756dc9e6928</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="8" t="inlineStr">
+        <is>
+          <t>7072025</t>
+        </is>
+      </c>
+      <c r="B1296" s="8" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Денис Александров</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>ООО «ДиВиГрупп»</t>
+        </is>
+      </c>
+      <c r="E1296" s="8" t="inlineStr">
+        <is>
+          <t>7726429829</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>ООО "ЭККО-РОС"</t>
+        </is>
+      </c>
+      <c r="G1296" s="8" t="inlineStr">
+        <is>
+          <t>5042013346</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1296" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1296" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1296" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1296" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1296" t="n">
+        <v>272524</v>
+      </c>
+      <c r="P1296" s="8" t="inlineStr">
+        <is>
+          <t>8c83faf4-48f1-4bce-96ed-5882ccb5be05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="8" t="inlineStr">
+        <is>
+          <t>АД/НЮ-СЗТК</t>
+        </is>
+      </c>
+      <c r="B1297" s="8" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Yulia Vydai</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>ООО "НЕГА ЮГ"</t>
+        </is>
+      </c>
+      <c r="E1297" s="8" t="inlineStr">
+        <is>
+          <t>2304051152</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>ООО "СПЕЦИАЛИЗИРОВАННЫЙ ЗАСТРОЙЩИК "ТЕРРИТОРИЯ КОМФОРТА"</t>
+        </is>
+      </c>
+      <c r="G1297" s="8" t="inlineStr">
+        <is>
+          <t>7708333271</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1297" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1297" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1297" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1297" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1297" t="n">
+        <v>257794</v>
+      </c>
+      <c r="P1297" s="8" t="inlineStr">
+        <is>
+          <t>08ca60ae-0ff8-4eb7-a32e-70e88191e323</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="8" t="inlineStr">
+        <is>
+          <t>АД/НЮ-СЗГОЛДФИШ</t>
+        </is>
+      </c>
+      <c r="B1298" s="8" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Yulia Vydai</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>ООО "НЕГА ЮГ"</t>
+        </is>
+      </c>
+      <c r="E1298" s="8" t="inlineStr">
+        <is>
+          <t>2304051152</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>АО "СПЕЦИАЛИЗИРОВАННЫЙ ЗАСТРОЙЩИК ГОЛДФИШ"</t>
+        </is>
+      </c>
+      <c r="G1298" s="8" t="inlineStr">
+        <is>
+          <t>7709733836</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1298" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1298" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1298" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1298" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1298" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1298" t="n">
+        <v>272864</v>
+      </c>
+      <c r="P1298" s="8" t="inlineStr">
+        <is>
+          <t>05cfe5bf-03e2-4b88-b43d-d39da7bd5a7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="8" t="inlineStr">
+        <is>
+          <t>АД/НЮ-СЗЩиброво</t>
+        </is>
+      </c>
+      <c r="B1299" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Yulia Vydai</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>ООО "НЕГА ЮГ"</t>
+        </is>
+      </c>
+      <c r="E1299" s="8" t="inlineStr">
+        <is>
+          <t>2304051152</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>ООО "СЗ ЩИБРОВО"</t>
+        </is>
+      </c>
+      <c r="G1299" s="8" t="inlineStr">
+        <is>
+          <t>9701058929</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1299" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1299" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1299" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1299" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1299" t="n">
+        <v>273096</v>
+      </c>
+      <c r="P1299" s="8" t="inlineStr">
+        <is>
+          <t>2045dbca-b6bb-4227-899a-db7306a884a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="8" t="inlineStr">
+        <is>
+          <t>64/РА</t>
+        </is>
+      </c>
+      <c r="B1300" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Елизавета Негуляева</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>ООО «МЕГАБАЙТ»</t>
+        </is>
+      </c>
+      <c r="E1300" s="8" t="inlineStr">
+        <is>
+          <t>9717094351</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>АО "ТАНДЕР"</t>
+        </is>
+      </c>
+      <c r="G1300" s="8" t="inlineStr">
+        <is>
+          <t>2310031475</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1300" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1300" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1300" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1300" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1300" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1300" t="n">
+        <v>272348</v>
+      </c>
+      <c r="P1300" s="8" t="inlineStr">
+        <is>
+          <t>31642a27-e133-4048-b816-30c72911f6df</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="8" t="inlineStr">
+        <is>
+          <t>21/2026</t>
+        </is>
+      </c>
+      <c r="B1301" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Елизавета Негуляева</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>АО «Медиа Инстинкт»</t>
+        </is>
+      </c>
+      <c r="E1301" s="8" t="inlineStr">
+        <is>
+          <t>7714760793</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>ООО "Специализированный застройщик "Дубининская 59"</t>
+        </is>
+      </c>
+      <c r="G1301" s="8" t="inlineStr">
+        <is>
+          <t>9705121762</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1301" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1301" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1301" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1301" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1301" t="n">
+        <v>270458</v>
+      </c>
+      <c r="P1301" s="8" t="inlineStr">
+        <is>
+          <t>32610469-43d6-4d47-b2d3-ed25b21eed5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="8" t="inlineStr">
+        <is>
+          <t>6/2016</t>
+        </is>
+      </c>
+      <c r="B1302" s="8" t="inlineStr">
+        <is>
+          <t>2016-05-04</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Арина Костюшина</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>ООО «Управляющая компания «Аура»</t>
+        </is>
+      </c>
+      <c r="E1302" s="8" t="inlineStr">
+        <is>
+          <t>7728564189</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>ООО "НСТ"</t>
+        </is>
+      </c>
+      <c r="G1302" s="8" t="inlineStr">
+        <is>
+          <t>7726341892</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1302" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1302" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1302" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1302" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1302" t="n">
+        <v>272581</v>
+      </c>
+      <c r="P1302" s="8" t="inlineStr">
+        <is>
+          <t>0b4c57cc-df43-4858-b28a-d61f403ff8c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="8" t="inlineStr">
+        <is>
+          <t>15/12/2018</t>
+        </is>
+      </c>
+      <c r="B1303" s="8" t="inlineStr">
+        <is>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Anastasia Tokareva</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>ООО "ДНС Ритейл"</t>
+        </is>
+      </c>
+      <c r="E1303" s="8" t="inlineStr">
+        <is>
+          <t>2540167061</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>ООО «Ориент Хоусхолд Апплиансес»</t>
+        </is>
+      </c>
+      <c r="G1303" s="8" t="inlineStr">
+        <is>
+          <t>7714702390</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1303" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1303" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1303" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1303" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1303" t="n">
+        <v>272684</v>
+      </c>
+      <c r="P1303" s="8" t="inlineStr">
+        <is>
+          <t>26d95ca5-aeb1-48b6-aa10-309ce6460f52</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="8" t="inlineStr">
+        <is>
+          <t>1164/2025</t>
+        </is>
+      </c>
+      <c r="B1304" s="8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Роман Сарычев</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>ООО УК «Нектарин»</t>
+        </is>
+      </c>
+      <c r="E1304" s="8" t="inlineStr">
+        <is>
+          <t>7710703730</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>ООО "ЛОТТЕ ЧИЛЬ СОНГ БЕВЕРИДЖ РУС"</t>
+        </is>
+      </c>
+      <c r="G1304" s="8" t="inlineStr">
+        <is>
+          <t>9728122498</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1304" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1304" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1304" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1304" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1304" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1304" t="n">
+        <v>268910</v>
+      </c>
+      <c r="P1304" s="8" t="inlineStr">
+        <is>
+          <t>a1df842a-112f-44ad-b1e9-24c8103d8b04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="8" t="inlineStr">
+        <is>
+          <t>СЗГ-0505</t>
+        </is>
+      </c>
+      <c r="B1305" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Ольга Панова</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>ООО "АДВЕЛОП"</t>
+        </is>
+      </c>
+      <c r="E1305" s="8" t="inlineStr">
+        <is>
+          <t>7725356230</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>ООО "СЗ "ГРОДНЕНСКАЯ 18"</t>
+        </is>
+      </c>
+      <c r="G1305" s="8" t="inlineStr">
+        <is>
+          <t>7731541953</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1305" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1305" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1305" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1305" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1305" t="n">
+        <v>272896</v>
+      </c>
+      <c r="P1305" s="8" t="inlineStr">
+        <is>
+          <t>9bc489c0-4897-49ae-8883-893acd6b0494</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="8" t="inlineStr">
+        <is>
+          <t>200624</t>
+        </is>
+      </c>
+      <c r="B1306" s="8" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Yulia Bezinskih</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>ООО «Брендинг Лаборатория»</t>
+        </is>
+      </c>
+      <c r="E1306" s="8" t="inlineStr">
+        <is>
+          <t>7701951818</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>АО "СЕВЕРСТАЛЬ МЕНЕДЖМЕНТ"</t>
+        </is>
+      </c>
+      <c r="G1306" s="8" t="inlineStr">
+        <is>
+          <t>7713505053</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1306" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1306" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1306" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1306" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1306" t="n">
+        <v>273187</v>
+      </c>
+      <c r="P1306" s="8" t="inlineStr">
+        <is>
+          <t>1520e349-68f3-4be0-9ebe-34a43eec5150</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="8" t="inlineStr">
+        <is>
+          <t>07/2024</t>
+        </is>
+      </c>
+      <c r="B1307" s="8" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Надежда Рашковецкая</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>АО «Медиа Инстинкт»</t>
+        </is>
+      </c>
+      <c r="E1307" s="8" t="inlineStr">
+        <is>
+          <t>7714760793</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>ООО "ГК "ИННОТЕХ"</t>
+        </is>
+      </c>
+      <c r="G1307" s="8" t="inlineStr">
+        <is>
+          <t>9703073496</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1307" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1307" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1307" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1307" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1307" t="n">
+        <v>272930</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="8" t="inlineStr">
+        <is>
+          <t>02/3006-26</t>
+        </is>
+      </c>
+      <c r="B1308" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Арина Костюшина</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>ООО «С-МАРКЕТИНГ»</t>
+        </is>
+      </c>
+      <c r="E1308" s="8" t="inlineStr">
+        <is>
+          <t>7736319695</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>ООО "КБП"</t>
+        </is>
+      </c>
+      <c r="G1308" s="8" t="inlineStr">
+        <is>
+          <t>9725063452</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1308" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1308" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1308" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1308" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1308" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1308" t="n">
+        <v>273031</v>
+      </c>
+      <c r="P1308" s="8" t="inlineStr">
+        <is>
+          <t>d655f45e-df80-41d2-9bf6-2caeb6ef1f0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="8" t="inlineStr">
+        <is>
+          <t>21/2023</t>
+        </is>
+      </c>
+      <c r="B1309" s="8" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Надежда Рашковецкая</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>АО «Медиа Инстинкт»</t>
+        </is>
+      </c>
+      <c r="E1309" s="8" t="inlineStr">
+        <is>
+          <t>7714760793</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>ООО «Маревен Фуд Сэнтрал»</t>
+        </is>
+      </c>
+      <c r="G1309" s="8" t="inlineStr">
+        <is>
+          <t>5077018948</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1309" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1309" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1309" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1309" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1309" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1309" t="n">
+        <v>273037</v>
+      </c>
+      <c r="P1309" s="8" t="inlineStr">
+        <is>
+          <t>8777b82e-b4f2-4736-ae7e-25add09a7681</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="8" t="inlineStr">
+        <is>
+          <t>10/1/2025</t>
+        </is>
+      </c>
+      <c r="B1310" s="8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Елизавета Негуляева</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>ООО «Хорайзн Медиа»</t>
+        </is>
+      </c>
+      <c r="E1310" s="8" t="inlineStr">
+        <is>
+          <t>7731463631</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>ООО "ГРИНЛАЙТ"</t>
+        </is>
+      </c>
+      <c r="G1310" s="8" t="inlineStr">
+        <is>
+          <t>5401359124</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1310" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1310" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1310" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1310" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1310" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1310" t="n">
+        <v>214462</v>
+      </c>
+      <c r="P1310" s="8" t="inlineStr">
+        <is>
+          <t>18eb9da8-1867-4e6d-abed-2341e4c3610c</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="8" t="inlineStr">
+        <is>
+          <t>18/06/26</t>
+        </is>
+      </c>
+      <c r="B1311" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>ИП Бурундуков В.А.</t>
+        </is>
+      </c>
+      <c r="E1311" s="8" t="inlineStr">
+        <is>
+          <t>665914948345</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>ООО "ЛОГОСОФТ"</t>
+        </is>
+      </c>
+      <c r="G1311" s="8" t="inlineStr">
+        <is>
+          <t>5009112893</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1311" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1311" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1311" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1311" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1311" t="n">
+        <v>276000</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="8" t="inlineStr">
+        <is>
+          <t>№ 1219/2026</t>
+        </is>
+      </c>
+      <c r="B1312" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Анна Кочукова</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью Управляющая компания "Нектарин"</t>
+        </is>
+      </c>
+      <c r="E1312" s="8" t="inlineStr">
+        <is>
+          <t>7710703730</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>ООО "ЛОТТЕ ЧИЛЬ СОНГ БЕВЕРИДЖ РУС"</t>
+        </is>
+      </c>
+      <c r="G1312" s="8" t="inlineStr">
+        <is>
+          <t>9728122498</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1312" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1312" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1312" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1312" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1312" t="n">
+        <v>273407</v>
+      </c>
+      <c r="P1312" s="8" t="inlineStr">
+        <is>
+          <t>7e1d8f4f-4c5a-48eb-bc7b-38a503147918</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="8" t="inlineStr">
+        <is>
+          <t>№ 1217/2026</t>
+        </is>
+      </c>
+      <c r="B1313" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Анна Кочукова</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью Управляющая компания "Нектарин"</t>
+        </is>
+      </c>
+      <c r="E1313" s="8" t="inlineStr">
+        <is>
+          <t>7710703730</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>ООО "Профессиональный конный альянс"</t>
+        </is>
+      </c>
+      <c r="G1313" s="8" t="inlineStr">
+        <is>
+          <t>9703232594</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1313" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1313" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1313" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1313" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1313" t="n">
+        <v>273455</v>
+      </c>
+      <c r="P1313" s="8" t="inlineStr">
+        <is>
+          <t>04b3c6d1-6dcc-4763-9821-9107026526a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="8" t="inlineStr">
+        <is>
+          <t>А-05/26-46</t>
+        </is>
+      </c>
+      <c r="B1314" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Ольга Панова</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>ООО «Арт-Композишн»</t>
+        </is>
+      </c>
+      <c r="E1314" s="8" t="inlineStr">
+        <is>
+          <t>7701260183</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>ООО "ФК ГРАНД КАПИТАЛ"</t>
+        </is>
+      </c>
+      <c r="G1314" s="8" t="inlineStr">
+        <is>
+          <t>7729418511</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1314" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1314" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1314" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1314" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1314" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1314" t="n">
+        <v>273481</v>
+      </c>
+      <c r="P1314" s="8" t="inlineStr">
+        <is>
+          <t>51af09ac-5bab-4395-9a01-e2e57314a132</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="8" t="inlineStr">
+        <is>
+          <t>1223/2026</t>
+        </is>
+      </c>
+      <c r="B1315" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>ООО УК «Нектарин»</t>
+        </is>
+      </c>
+      <c r="E1315" s="8" t="inlineStr">
+        <is>
+          <t>7710703730</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>АО "СЗ "Лайф Павелецкая"</t>
+        </is>
+      </c>
+      <c r="G1315" s="8" t="inlineStr">
+        <is>
+          <t>7717577210</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1315" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1315" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1315" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1315" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1315" t="n">
+        <v>273878</v>
+      </c>
+      <c r="P1315" s="8" t="inlineStr">
+        <is>
+          <t>e381e8f7-8726-4bcb-9e47-e6bc06bd0247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="8" t="inlineStr">
+        <is>
+          <t>Mpc-292</t>
+        </is>
+      </c>
+      <c r="B1316" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Ольга Панова</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>ООО "МЕДИАПЛАН КОНСАЛТИНГ"</t>
+        </is>
+      </c>
+      <c r="E1316" s="8" t="inlineStr">
+        <is>
+          <t>7726462336</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>ООО "ЭСТЕО РУС"</t>
+        </is>
+      </c>
+      <c r="G1316" s="8" t="inlineStr">
+        <is>
+          <t>7743487147</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1316" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1316" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1316" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1316" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1316" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1316" t="n">
+        <v>273584</v>
+      </c>
+      <c r="P1316" s="8" t="inlineStr">
+        <is>
+          <t>b56a389a-a2e2-4f1a-a771-5c4ded76f17b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="8" t="inlineStr">
+        <is>
+          <t>Ак-1012/2025-01</t>
+        </is>
+      </c>
+      <c r="B1317" s="8" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Ольга Панова</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>ООО "Адвентум Консалтинг"</t>
+        </is>
+      </c>
+      <c r="E1317" s="8" t="inlineStr">
+        <is>
+          <t>7717720559</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>ООО "СЗ "ЖК ЯРКИЙ. РИГА"</t>
+        </is>
+      </c>
+      <c r="G1317" s="8" t="inlineStr">
+        <is>
+          <t>5024214427</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1317" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1317" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1317" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1317" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1317" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1317" t="n">
+        <v>273667</v>
+      </c>
+      <c r="P1317" s="8" t="inlineStr">
+        <is>
+          <t>1c727ccb-7a19-4a4b-8022-e1a06c8839c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="8" t="inlineStr">
+        <is>
+          <t>36/2024</t>
+        </is>
+      </c>
+      <c r="B1318" s="8" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Дарья Глебова</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>ООО "МЕДИА ТРАСТ"</t>
+        </is>
+      </c>
+      <c r="E1318" s="8" t="inlineStr">
+        <is>
+          <t>9731017581</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>АО "РЕННА-ХОЛДИНГ"</t>
+        </is>
+      </c>
+      <c r="G1318" s="8" t="inlineStr">
+        <is>
+          <t>7721242760</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1318" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1318" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1318" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1318" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1318" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1318" t="n">
+        <v>274568</v>
+      </c>
+      <c r="P1318" s="8" t="inlineStr">
+        <is>
+          <t>56beb469-fc60-4462-bb90-90f28c48ef6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="8" t="inlineStr">
+        <is>
+          <t>24/2026</t>
+        </is>
+      </c>
+      <c r="B1319" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Елизавета Негуляева</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>АО «Медиа Инстинкт»</t>
+        </is>
+      </c>
+      <c r="E1319" s="8" t="inlineStr">
+        <is>
+          <t>7714760793</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>ООО Специализированный застройщик "Левел Академическая"</t>
+        </is>
+      </c>
+      <c r="G1319" s="8" t="inlineStr">
+        <is>
+          <t>9705108088</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1319" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1319" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1319" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1319" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1319" t="n">
+        <v>273750</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="8" t="inlineStr">
+        <is>
+          <t>05/03/2026-01</t>
+        </is>
+      </c>
+      <c r="B1320" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Надежда Рашковецкая</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>ООО "ЭмДжиКом"</t>
+        </is>
+      </c>
+      <c r="E1320" s="8" t="inlineStr">
+        <is>
+          <t>7725560073</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>ООО "Специализированный Застройщик "Ч-Девелопмент"</t>
+        </is>
+      </c>
+      <c r="G1320" s="8" t="inlineStr">
+        <is>
+          <t>7726478110</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1320" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1320" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1320" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1320" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1320" t="n">
+        <v>273790</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1321" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1321" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>ООО "ВК"</t>
+        </is>
+      </c>
+      <c r="G1321" s="8" t="inlineStr">
+        <is>
+          <t>7743001840</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1321" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1321" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1321" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1321" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1321" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q1321" s="8" t="inlineStr">
+        <is>
+          <t>72ea8625-77fb-42c1-90c1-dd4a796c2cfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1322" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>ООО «Звезда ЦИ»</t>
+        </is>
+      </c>
+      <c r="E1322" s="8" t="inlineStr">
+        <is>
+          <t>9709030065</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>АО «Премьер-Фарма»</t>
+        </is>
+      </c>
+      <c r="G1322" s="8" t="inlineStr">
+        <is>
+          <t>9701157101</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1322" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1322" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1322" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1322" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1322" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1322" t="n">
+        <v>274017</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1323" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1323" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>ООО "ВК"</t>
+        </is>
+      </c>
+      <c r="G1323" s="8" t="inlineStr">
+        <is>
+          <t>7743001840</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1323" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1323" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1323" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1323" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q1323" s="8" t="inlineStr">
+        <is>
+          <t>17ef4cbf-71ee-45a9-b5e4-1c5e8581a951</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="8" t="inlineStr">
+        <is>
+          <t>01/2022</t>
+        </is>
+      </c>
+      <c r="B1324" s="8" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Надежда Рашковецкая</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>ООО "Мера Русс Медиа"</t>
+        </is>
+      </c>
+      <c r="E1324" s="8" t="inlineStr">
+        <is>
+          <t>7717707438</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>"Цифра Брокер"</t>
+        </is>
+      </c>
+      <c r="G1324" s="8" t="inlineStr">
+        <is>
+          <t>7705934210</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1324" s="8" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="K1324" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1324" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1324" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1324" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1324" t="n">
+        <v>268491</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="8" t="inlineStr">
+        <is>
+          <t>ИА-2020/2/11</t>
+        </is>
+      </c>
+      <c r="B1325" s="8" t="inlineStr">
+        <is>
+          <t>2020-02-25</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>ООО "ИА РиалВеб"</t>
+        </is>
+      </c>
+      <c r="E1325" s="8" t="inlineStr">
+        <is>
+          <t>7813323882</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>ООО "БИОНОРИКА"</t>
+        </is>
+      </c>
+      <c r="G1325" s="8" t="inlineStr">
+        <is>
+          <t>7729590470</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1325" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1325" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1325" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1325" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1325" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1325" t="n">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1326" s="8" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Anastasia Tokareva</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>ООО "ДРИМ МЕДИА"</t>
+        </is>
+      </c>
+      <c r="E1326" s="8" t="inlineStr">
+        <is>
+          <t>9717159834</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>ООО "ДОКТОР 03"</t>
+        </is>
+      </c>
+      <c r="G1326" s="8" t="inlineStr">
+        <is>
+          <t>7722745206</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1326" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1326" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1326" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1326" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1326" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1326" t="n">
+        <v>270543</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B1327" s="8" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Виолетта Мацюшевская</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>ООО "АПР Евразия"</t>
+        </is>
+      </c>
+      <c r="E1327" s="8" t="inlineStr">
+        <is>
+          <t>7708547932</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>АО "Акрихин"</t>
+        </is>
+      </c>
+      <c r="G1327" s="8" t="inlineStr">
+        <is>
+          <t>5031013320</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1327" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1327" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1327" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1327" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1327" t="n">
+        <v>246066</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="8" t="inlineStr">
+        <is>
+          <t>ЗСТР/2026-22</t>
+        </is>
+      </c>
+      <c r="B1328" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Арина Костюшина</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>ООО «Уайт Бокс Медиа»</t>
+        </is>
+      </c>
+      <c r="E1328" s="8" t="inlineStr">
+        <is>
+          <t>9731048741</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>ООО "СЗ "Б-ХОЛДИНГ"</t>
+        </is>
+      </c>
+      <c r="G1328" s="8" t="inlineStr">
+        <is>
+          <t>9704010040</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1328" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1328" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1328" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1328" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1328" t="n">
+        <v>275725</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="8" t="inlineStr">
+        <is>
+          <t>№ 1197/2026</t>
+        </is>
+      </c>
+      <c r="B1329" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Anastasia Tokareva</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>ООО УК «Нектарин»</t>
+        </is>
+      </c>
+      <c r="E1329" s="8" t="inlineStr">
+        <is>
+          <t>7710703730</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>АО "МЯСОКОМБИНАТ КЛИНСКИЙ"</t>
+        </is>
+      </c>
+      <c r="G1329" s="8" t="inlineStr">
+        <is>
+          <t>5020002260</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1329" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1329" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1329" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1329" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1329" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1329" t="n">
+        <v>275506</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="8" t="inlineStr">
+        <is>
+          <t>25/2026</t>
+        </is>
+      </c>
+      <c r="B1330" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>АО «Медиа Инстинкт»</t>
+        </is>
+      </c>
+      <c r="E1330" s="8" t="inlineStr">
+        <is>
+          <t>7714760793</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>ООО СЗ "ЛЕВЕЛ СВОБОДЫ"</t>
+        </is>
+      </c>
+      <c r="G1330" s="8" t="inlineStr">
+        <is>
+          <t>9705213484</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1330" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1330" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1330" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1330" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1330" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1330" t="n">
+        <v>270548</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="8" t="inlineStr">
+        <is>
+          <t>18.09.2025</t>
+        </is>
+      </c>
+      <c r="B1331" s="8" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>OOO «ФОРМА»</t>
+        </is>
+      </c>
+      <c r="E1331" s="8" t="inlineStr">
+        <is>
+          <t>7729604691</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>ООО "СЗ "КРТ ВОЛОКОЛАМСКОЕ"</t>
+        </is>
+      </c>
+      <c r="G1331" s="8" t="inlineStr">
+        <is>
+          <t>9723238548</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1331" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1331" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1331" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1331" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1331" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1331" t="n">
+        <v>275399</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="8" t="inlineStr">
+        <is>
+          <t>Adv-032</t>
+        </is>
+      </c>
+      <c r="B1332" s="8" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Анна Кочукова</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>ООО «Агентство Трафик»</t>
+        </is>
+      </c>
+      <c r="E1332" s="8" t="inlineStr">
+        <is>
+          <t>7804452480</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>ООО "Хантинг"</t>
+        </is>
+      </c>
+      <c r="G1332" s="8" t="inlineStr">
+        <is>
+          <t>3319006860</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1332" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1332" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1332" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1332" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1332" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1332" t="n">
+        <v>276814</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="8" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="B1333" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Елизавета Седых</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>ООО  "ОККАМ ИКС"</t>
+        </is>
+      </c>
+      <c r="E1333" s="8" t="inlineStr">
+        <is>
+          <t>7731596504</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>ООО «Ювелирная группа «АЛРОСА»</t>
+        </is>
+      </c>
+      <c r="G1333" s="8" t="inlineStr">
+        <is>
+          <t>6731040514</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1333" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1333" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1333" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1333" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1333" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1333" t="n">
+        <v>275401</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="8" t="inlineStr">
+        <is>
+          <t>19/2026</t>
+        </is>
+      </c>
+      <c r="B1334" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>АО «Медиа Инстинкт»</t>
+        </is>
+      </c>
+      <c r="E1334" s="8" t="inlineStr">
+        <is>
+          <t>7714760793</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>ООО СЗ "ВЕКТОР ДВИЖЕНИЯ"</t>
+        </is>
+      </c>
+      <c r="G1334" s="8" t="inlineStr">
+        <is>
+          <t>9705149542</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1334" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1334" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1334" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1334" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1334" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1334" t="n">
+        <v>274417</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="8" t="inlineStr">
+        <is>
+          <t>77-0526-КЭФ-117</t>
+        </is>
+      </c>
+      <c r="B1335" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>ООО «РА «СА МЕДИА»</t>
+        </is>
+      </c>
+      <c r="E1335" s="8" t="inlineStr">
+        <is>
+          <t>7710899410</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>ФОНД РЕНОВАЦИИ</t>
+        </is>
+      </c>
+      <c r="G1335" s="8" t="inlineStr">
+        <is>
+          <t>7703434808</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1335" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1335" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1335" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1335" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1335" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1335" t="n">
+        <v>272964</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="8" t="inlineStr">
+        <is>
+          <t>Thu Jan 30 2025 00:00:00 GMT+0300 (Москва, стандартное время)</t>
+        </is>
+      </c>
+      <c r="B1336" s="8" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>ООО "АДВЕЛОП"</t>
+        </is>
+      </c>
+      <c r="E1336" s="8" t="inlineStr">
+        <is>
+          <t>7725356230</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>ООО "Специализированный Застройщик "Искра"</t>
+        </is>
+      </c>
+      <c r="G1336" s="8" t="inlineStr">
+        <is>
+          <t>7703429621</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1336" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1336" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1336" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1336" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1336" t="n">
+        <v>182673</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="8" t="inlineStr">
+        <is>
+          <t>Thu Jan 30 2025 00:00:00 GMT+0300 (Москва, стандартное время)</t>
+        </is>
+      </c>
+      <c r="B1337" s="8" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>ООО "АДВЕЛОП"</t>
+        </is>
+      </c>
+      <c r="E1337" s="8" t="inlineStr">
+        <is>
+          <t>7725356230</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>ООО "СЗ "РОДИНА ПЕРЕДЕЛКИНО"</t>
+        </is>
+      </c>
+      <c r="G1337" s="8" t="inlineStr">
+        <is>
+          <t>9717117697</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1337" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1337" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1337" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1337" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1337" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="8" t="inlineStr">
+        <is>
+          <t>ЗСТР/2026-19</t>
+        </is>
+      </c>
+      <c r="B1338" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Арина Костюшина</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>ООО «Уайт Бокс Медиа»</t>
+        </is>
+      </c>
+      <c r="E1338" s="8" t="inlineStr">
+        <is>
+          <t>9731048741</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>АО "СПЕЦИАЛИЗИРОВАННЫЙ ЗАСТРОЙЩИК ТПУ "ЛЕСОПАРКОВАЯ"</t>
+        </is>
+      </c>
+      <c r="G1338" s="8" t="inlineStr">
+        <is>
+          <t>7701387380</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1338" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1338" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1338" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1338" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1338" t="n">
+        <v>275768</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="8" t="inlineStr">
+        <is>
+          <t>04223/25</t>
+        </is>
+      </c>
+      <c r="B1339" s="8" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Виолетта Мацюшевская</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>«МедиаПлан»</t>
+        </is>
+      </c>
+      <c r="E1339" s="8" t="inlineStr">
+        <is>
+          <t>7702703504</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>АО "ЦВ "Протек"</t>
+        </is>
+      </c>
+      <c r="G1339" s="8" t="inlineStr">
+        <is>
+          <t>7724053916</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1339" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1339" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1339" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1339" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1339" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1339" t="n">
+        <v>275504</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="8" t="inlineStr">
+        <is>
+          <t>250601-РП</t>
+        </is>
+      </c>
+      <c r="B1340" s="8" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Anastasia Tokareva</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>ООО "АДВЕЛОП"</t>
+        </is>
+      </c>
+      <c r="E1340" s="8" t="inlineStr">
+        <is>
+          <t>7725356230</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>ООО "СЗ "РОДИНА ПЕРЕДЕЛКИНО"</t>
+        </is>
+      </c>
+      <c r="G1340" s="8" t="inlineStr">
+        <is>
+          <t>9717117697</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1340" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1340" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1340" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1340" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1340" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1340" t="n">
+        <v>275522</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="8" t="inlineStr">
+        <is>
+          <t>GWMR-A11-0726</t>
+        </is>
+      </c>
+      <c r="B1341" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Yulia Bezinskih</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>ООО "Мера Русс Медиа"</t>
+        </is>
+      </c>
+      <c r="E1341" s="8" t="inlineStr">
+        <is>
+          <t>7717707438</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>ООО "Грейт Волл Мотор Рус"</t>
+        </is>
+      </c>
+      <c r="G1341" s="8" t="inlineStr">
+        <is>
+          <t>7729763331</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1341" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1341" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1341" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1341" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1341" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1341" t="n">
+        <v>275625</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="8" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="B1342" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Елена Потапова</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>ООО "Инишитив РУС"</t>
+        </is>
+      </c>
+      <c r="E1342" s="8" t="inlineStr">
+        <is>
+          <t>7704231173</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>ООО "ТОСОЛ-СИНТЕЗ ТРЕЙДИНГ"</t>
+        </is>
+      </c>
+      <c r="G1342" s="8" t="inlineStr">
+        <is>
+          <t>5249046147</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1342" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1342" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1342" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1342" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1342" t="n">
+        <v>275761</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="8" t="inlineStr">
+        <is>
+          <t>К-01/2022</t>
+        </is>
+      </c>
+      <c r="B1343" s="8" t="inlineStr">
+        <is>
+          <t>2021-12-07</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>ООО "Мера Русс Медиа"</t>
+        </is>
+      </c>
+      <c r="E1343" s="8" t="inlineStr">
+        <is>
+          <t>7717707438</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>ООО "БИННОФАРМ ГРУПП"</t>
+        </is>
+      </c>
+      <c r="G1343" s="8" t="inlineStr">
+        <is>
+          <t>9704005675</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1343" s="8" t="inlineStr">
+        <is>
+          <t>Заключение договоров</t>
+        </is>
+      </c>
+      <c r="K1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1343" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1343" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1343" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1343" t="n">
+        <v>206248</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="8" t="inlineStr">
+        <is>
+          <t>26/01/01-03</t>
+        </is>
+      </c>
+      <c r="B1344" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Надежда Рашковецкая</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>ООО "ЭмДжиКом"</t>
+        </is>
+      </c>
+      <c r="E1344" s="8" t="inlineStr">
+        <is>
+          <t>7725560073</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>ООО "Специализированный Застройщик "Ч-Девелопмент"</t>
+        </is>
+      </c>
+      <c r="G1344" s="8" t="inlineStr">
+        <is>
+          <t>7726478110</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1344" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1344" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1344" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1344" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1344" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1344" t="n">
+        <v>276030</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="8" t="inlineStr">
+        <is>
+          <t>13CA0711</t>
+        </is>
+      </c>
+      <c r="B1345" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Yulia Vydai</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>АО "ПРОКСИМИТИ"</t>
+        </is>
+      </c>
+      <c r="E1345" s="8" t="inlineStr">
+        <is>
+          <t>7710586350</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>ООО "МВМ"</t>
+        </is>
+      </c>
+      <c r="G1345" s="8" t="inlineStr">
+        <is>
+          <t>7707548740</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1345" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1345" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1345" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1345" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1345" t="n">
+        <v>276963</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="8" t="inlineStr">
+        <is>
+          <t>13CA0711</t>
+        </is>
+      </c>
+      <c r="B1346" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Дарья Иванченко</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>АО "Проксимити"</t>
+        </is>
+      </c>
+      <c r="E1346" s="8" t="inlineStr">
+        <is>
+          <t>7710586350</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>ООО «‎Диджитал МДГ»‎‎</t>
+        </is>
+      </c>
+      <c r="G1346" s="8" t="inlineStr">
+        <is>
+          <t>9731077982</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>Посредничество</t>
+        </is>
+      </c>
+      <c r="J1346" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1346" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1346" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1346" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1346" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="8" t="inlineStr">
+        <is>
+          <t>Т-100123/1</t>
+        </is>
+      </c>
+      <c r="B1347" s="8" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Маргарита Воронова</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>ООО "СКАЙТЕК МЕДИА"</t>
+        </is>
+      </c>
+      <c r="E1347" s="8" t="inlineStr">
+        <is>
+          <t>7731385944</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>ООО ""ИНТЕРНЕТ РЕШЕНИЯ""</t>
+        </is>
+      </c>
+      <c r="G1347" s="8" t="inlineStr">
+        <is>
+          <t>7704217370</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1347" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1347" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1347" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1347" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1347" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1347" t="n">
+        <v>276981</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="8" t="inlineStr">
+        <is>
+          <t>7/2017</t>
+        </is>
+      </c>
+      <c r="B1348" s="8" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Надежда Рашковецкая</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>ООО «Управляющая компания «Аура»</t>
+        </is>
+      </c>
+      <c r="E1348" s="8" t="inlineStr">
+        <is>
+          <t>7728564189</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>ООО "ГПМ РАДИО"</t>
+        </is>
+      </c>
+      <c r="G1348" s="8" t="inlineStr">
+        <is>
+          <t>7714353188</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>Посреднический договор</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1348" s="8" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="K1348" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1348" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1348" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1348" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1348" t="n">
+        <v>276990</v>
+      </c>
+      <c r="P1348" s="8" t="inlineStr">
+        <is>
+          <t>ab3a5c26-9db2-4863-85e5-c2dda47aa84d</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1349" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1349" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>АО «БВТ БАРЬЕР РУС»</t>
+        </is>
+      </c>
+      <c r="G1349" s="8" t="inlineStr">
+        <is>
+          <t>5001017207</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1349" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1349" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1349" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1349" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1349" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1349" t="n">
+        <v>278097</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B1350" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1350" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>ООО "ВК"</t>
+        </is>
+      </c>
+      <c r="G1350" s="8" t="inlineStr">
+        <is>
+          <t>7743001840</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1350" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1350" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1350" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1350" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1350" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q1350" s="8" t="inlineStr">
+        <is>
+          <t>1d3fda1d-e3b8-49e9-b03c-e9a5823a79ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B1351" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1351" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>АО "ЭЙЧ ЭНД ЭН"</t>
+        </is>
+      </c>
+      <c r="G1351" s="8" t="inlineStr">
+        <is>
+          <t>7714626332</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1351" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1351" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1351" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1351" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1351" t="n">
+        <v>278057</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1352" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>ООО "ТРИ"</t>
+        </is>
+      </c>
+      <c r="E1352" s="8" t="inlineStr">
+        <is>
+          <t>6829155550</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>ООО "ВК"</t>
+        </is>
+      </c>
+      <c r="G1352" s="8" t="inlineStr">
+        <is>
+          <t>7743001840</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1352" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1352" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1352" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1352" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q1352" s="8" t="inlineStr">
+        <is>
+          <t>de41a666-d377-4b68-b61d-d5ebf1c770e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1353" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Девопс Девопс</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>ООО «Звезда ЦИ»</t>
+        </is>
+      </c>
+      <c r="E1353" s="8" t="inlineStr">
+        <is>
+          <t>9709030065</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>АО «Премьер-Фарма»</t>
+        </is>
+      </c>
+      <c r="G1353" s="8" t="inlineStr">
+        <is>
+          <t>9701157101</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>Доп. соглашение</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1353" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1353" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1353" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1353" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1353" t="n">
+        <v>278082</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="8" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="B1354" s="8" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Алиса Багрова</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>«МедиаПлан»</t>
+        </is>
+      </c>
+      <c r="E1354" s="8" t="inlineStr">
+        <is>
+          <t>7702703504</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>ООО «Нутриция»</t>
+        </is>
+      </c>
+      <c r="G1354" s="8" t="inlineStr">
+        <is>
+          <t>7705111270</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>Распространение рекламы</t>
+        </is>
+      </c>
+      <c r="J1354" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1354" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1354" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1354" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1354" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1354" t="n">
+        <v>278245</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="8" t="inlineStr">
+        <is>
+          <t>14/2026</t>
+        </is>
+      </c>
+      <c r="B1355" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Anastasia Tokareva</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>ООО «ГРЕЙТ ДИДЖИТАЛ М»</t>
+        </is>
+      </c>
+      <c r="E1355" s="8" t="inlineStr">
+        <is>
+          <t>7805806607</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>АО "ЛЕНСТРОЙТРЕСТ"</t>
+        </is>
+      </c>
+      <c r="G1355" s="8" t="inlineStr">
+        <is>
+          <t>7801082329</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1355" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1355" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1355" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1355" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="8" t="inlineStr">
+        <is>
+          <t>01/06/26-4 /1593/26</t>
+        </is>
+      </c>
+      <c r="B1356" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Kristina Vasilkova</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>ООО "ДЕЛЬТА-КЛИК"</t>
+        </is>
+      </c>
+      <c r="E1356" s="8" t="inlineStr">
+        <is>
+          <t>6685232610</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>АО "ПФ "СКБ Контур"</t>
+        </is>
+      </c>
+      <c r="G1356" s="8" t="inlineStr">
+        <is>
+          <t>6663003127</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>Договор на организацию распространения рекламы</t>
+        </is>
+      </c>
+      <c r="J1356" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K1356" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1356" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M1356" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="N1356" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O1356" t="n">
+        <v>278580</v>
       </c>
     </row>
   </sheetData>
